--- a/historico_pdf.xlsx
+++ b/historico_pdf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c35027b\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2E416C-5A2B-4878-9FAF-52AA4F02B110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E29C491-88D2-4822-AF5B-A27E54294396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="84">
   <si>
     <t>data_registro</t>
   </si>
@@ -73,7 +73,85 @@
     <t>moises</t>
   </si>
   <si>
+    <t>Argentina x Cabo Verde</t>
+  </si>
+  <si>
+    <t>Austrália x Egito</t>
+  </si>
+  <si>
+    <t>Suíça x Argélia</t>
+  </si>
+  <si>
+    <t>Portugal x Croácia</t>
+  </si>
+  <si>
+    <t>Espanha x Áustria</t>
+  </si>
+  <si>
+    <t>Estados Unidos x Bósnia e Herzegovina</t>
+  </si>
+  <si>
+    <t>Bélgica x Senegal</t>
+  </si>
+  <si>
+    <t>Inglaterra x Congo</t>
+  </si>
+  <si>
+    <t>México x Equador</t>
+  </si>
+  <si>
+    <t>Costa do Marfim x Noruega</t>
+  </si>
+  <si>
+    <t>França x Suécia</t>
+  </si>
+  <si>
+    <t>Holanda x Marrocos</t>
+  </si>
+  <si>
+    <t>Alemanha x Paraguai</t>
+  </si>
+  <si>
+    <t>Brasil x Japão</t>
+  </si>
+  <si>
+    <t>África do Sul x Canadá</t>
+  </si>
+  <si>
+    <t>Argélia x Áustria</t>
+  </si>
+  <si>
+    <t>Congo x Usbequistão</t>
+  </si>
+  <si>
+    <t>Jordânia x Argentina</t>
+  </si>
+  <si>
+    <t>Colômbia x Portugal</t>
+  </si>
+  <si>
+    <t>Panamá x Inglaterra</t>
+  </si>
+  <si>
+    <t>Croácia x Gana</t>
+  </si>
+  <si>
+    <t>Egito x Irã</t>
+  </si>
+  <si>
+    <t>Nova Zelândia x Bélgica</t>
+  </si>
+  <si>
+    <t>Cabo Verde x Arábia Saudita</t>
+  </si>
+  <si>
+    <t>Uruguai x Espanha</t>
+  </si>
+  <si>
     <t>Noruega x França</t>
+  </si>
+  <si>
+    <t>Senegal x Iraque</t>
   </si>
   <si>
     <t>Paraguai x Austrália</t>
@@ -562,14 +640,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E457"/>
+  <dimension ref="A1:E729"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -603,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -620,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -637,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -654,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -671,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -688,7 +766,7 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -705,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -722,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -739,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
@@ -756,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -773,7 +851,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -790,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -807,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -824,7 +902,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -841,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -858,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -875,7 +953,7 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -892,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -909,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -926,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -943,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -960,7 +1038,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -994,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1011,7 +1089,7 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1028,7 +1106,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
@@ -1045,7 +1123,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
@@ -1062,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
@@ -1079,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
@@ -1096,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1113,7 +1191,7 @@
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
@@ -1130,7 +1208,7 @@
         <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -1147,7 +1225,7 @@
         <v>2</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -1164,7 +1242,7 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -1181,7 +1259,7 @@
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
@@ -1198,7 +1276,7 @@
         <v>2</v>
       </c>
       <c r="E37" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
@@ -1215,7 +1293,7 @@
         <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
@@ -1232,7 +1310,7 @@
         <v>2</v>
       </c>
       <c r="E39" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
@@ -1249,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="E40" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
@@ -1266,7 +1344,7 @@
         <v>2</v>
       </c>
       <c r="E41" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.3">
@@ -1283,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -1300,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
@@ -1317,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.3">
@@ -1334,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
@@ -1351,7 +1429,7 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.3">
@@ -1368,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
@@ -1385,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
@@ -1402,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
@@ -1419,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
@@ -1436,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
@@ -1453,7 +1531,7 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
@@ -1470,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
@@ -1487,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
@@ -1504,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
@@ -1521,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
@@ -1538,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
@@ -1555,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -1572,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
@@ -1589,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
@@ -1606,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
@@ -1623,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
@@ -1640,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
@@ -1657,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
@@ -1674,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="E65" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
@@ -1691,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
@@ -1708,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
@@ -1725,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="E68" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
@@ -1742,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.3">
@@ -1759,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
@@ -1776,7 +1854,7 @@
         <v>1</v>
       </c>
       <c r="E71" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
@@ -1793,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="E72" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
@@ -1810,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
@@ -1827,7 +1905,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
@@ -1844,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
@@ -1861,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="E76" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.3">
@@ -1878,7 +1956,7 @@
         <v>2</v>
       </c>
       <c r="E77" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
@@ -1895,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.3">
@@ -1912,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
@@ -1929,7 +2007,7 @@
         <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
@@ -1946,7 +2024,7 @@
         <v>1</v>
       </c>
       <c r="E81" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.3">
@@ -1963,7 +2041,7 @@
         <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -1980,7 +2058,7 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.3">
@@ -1997,7 +2075,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.3">
@@ -2014,7 +2092,7 @@
         <v>2</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.3">
@@ -2031,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.3">
@@ -2048,7 +2126,7 @@
         <v>2</v>
       </c>
       <c r="E87" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
@@ -2065,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.3">
@@ -2079,7 +2157,7 @@
         <v>2</v>
       </c>
       <c r="E89" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.3">
@@ -2093,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -2107,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.3">
@@ -2121,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
@@ -2135,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.3">
@@ -2149,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
@@ -2163,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
@@ -2177,7 +2255,7 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.3">
@@ -2191,7 +2269,7 @@
         <v>1</v>
       </c>
       <c r="E97" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.3">
@@ -2205,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="E98" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.3">
@@ -2219,7 +2297,7 @@
         <v>0</v>
       </c>
       <c r="E99" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.3">
@@ -2233,7 +2311,7 @@
         <v>1</v>
       </c>
       <c r="E100" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.3">
@@ -2247,7 +2325,7 @@
         <v>2</v>
       </c>
       <c r="E101" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.3">
@@ -2261,7 +2339,7 @@
         <v>3</v>
       </c>
       <c r="E102" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.3">
@@ -2275,7 +2353,7 @@
         <v>2</v>
       </c>
       <c r="E103" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.3">
@@ -2289,7 +2367,7 @@
         <v>2</v>
       </c>
       <c r="E104" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.3">
@@ -2303,7 +2381,7 @@
         <v>2</v>
       </c>
       <c r="E105" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.3">
@@ -2317,7 +2395,7 @@
         <v>2</v>
       </c>
       <c r="E106" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.3">
@@ -2331,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.3">
@@ -2345,7 +2423,7 @@
         <v>2</v>
       </c>
       <c r="E108" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.3">
@@ -2359,7 +2437,7 @@
         <v>2</v>
       </c>
       <c r="E109" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.3">
@@ -2373,7 +2451,7 @@
         <v>2</v>
       </c>
       <c r="E110" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.3">
@@ -2387,7 +2465,7 @@
         <v>2</v>
       </c>
       <c r="E111" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.3">
@@ -2401,7 +2479,7 @@
         <v>0</v>
       </c>
       <c r="E112" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.3">
@@ -2415,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.3">
@@ -2429,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="E114" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.3">
@@ -2443,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="E115" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.3">
@@ -2457,7 +2535,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.3">
@@ -2471,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.3">
@@ -2485,7 +2563,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.3">
@@ -2499,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.3">
@@ -2513,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="E120" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.3">
@@ -2527,7 +2605,7 @@
         <v>1</v>
       </c>
       <c r="E121" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.3">
@@ -2541,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="E122" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.3">
@@ -2555,7 +2633,7 @@
         <v>1</v>
       </c>
       <c r="E123" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.3">
@@ -2569,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="E124" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.3">
@@ -2583,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="E125" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.3">
@@ -2597,7 +2675,7 @@
         <v>1</v>
       </c>
       <c r="E126" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.3">
@@ -2611,7 +2689,7 @@
         <v>2</v>
       </c>
       <c r="E127" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.3">
@@ -2625,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="E128" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.3">
@@ -2639,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="E129" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.3">
@@ -2653,7 +2731,7 @@
         <v>2</v>
       </c>
       <c r="E130" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.3">
@@ -2667,7 +2745,7 @@
         <v>1</v>
       </c>
       <c r="E131" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.3">
@@ -2681,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="E132" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.3">
@@ -2695,7 +2773,7 @@
         <v>2</v>
       </c>
       <c r="E133" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.3">
@@ -2709,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="E134" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.3">
@@ -2723,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="E135" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="136" spans="2:5" x14ac:dyDescent="0.3">
@@ -2737,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="E136" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.3">
@@ -2751,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="E137" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.3">
@@ -2765,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="E138" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.3">
@@ -2779,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="140" spans="2:5" x14ac:dyDescent="0.3">
@@ -2793,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="E140" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="141" spans="2:5" x14ac:dyDescent="0.3">
@@ -2807,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="142" spans="2:5" x14ac:dyDescent="0.3">
@@ -2821,7 +2899,7 @@
         <v>1</v>
       </c>
       <c r="E142" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.3">
@@ -2835,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="E143" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.3">
@@ -2849,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="E144" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.3">
@@ -2863,7 +2941,7 @@
         <v>2</v>
       </c>
       <c r="E145" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.3">
@@ -2877,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="E146" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.3">
@@ -2891,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.3">
@@ -2905,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="E148" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.3">
@@ -2919,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="E149" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.3">
@@ -2933,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="E150" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.3">
@@ -2947,7 +3025,7 @@
         <v>1</v>
       </c>
       <c r="E151" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.3">
@@ -2961,7 +3039,7 @@
         <v>0</v>
       </c>
       <c r="E152" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.3">
@@ -2975,7 +3053,7 @@
         <v>1</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.3">
@@ -2989,7 +3067,7 @@
         <v>0</v>
       </c>
       <c r="E154" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.3">
@@ -3003,7 +3081,7 @@
         <v>1</v>
       </c>
       <c r="E155" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.3">
@@ -3017,7 +3095,7 @@
         <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.3">
@@ -3031,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="E157" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.3">
@@ -3045,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="E158" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.3">
@@ -3059,7 +3137,7 @@
         <v>0</v>
       </c>
       <c r="E159" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.3">
@@ -3073,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="E160" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.3">
@@ -3087,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="E161" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.3">
@@ -3101,7 +3179,7 @@
         <v>1</v>
       </c>
       <c r="E162" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.3">
@@ -3115,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="E163" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.3">
@@ -3129,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="E164" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.3">
@@ -3143,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="E165" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.3">
@@ -3157,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="E166" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.3">
@@ -3171,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="E167" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.3">
@@ -3185,7 +3263,7 @@
         <v>3</v>
       </c>
       <c r="E168" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.3">
@@ -3199,7 +3277,7 @@
         <v>2</v>
       </c>
       <c r="E169" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.3">
@@ -3213,7 +3291,7 @@
         <v>3</v>
       </c>
       <c r="E170" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.3">
@@ -3227,7 +3305,7 @@
         <v>4</v>
       </c>
       <c r="E171" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.3">
@@ -3241,7 +3319,7 @@
         <v>1</v>
       </c>
       <c r="E172" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.3">
@@ -3255,7 +3333,7 @@
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174" spans="2:5" x14ac:dyDescent="0.3">
@@ -3269,7 +3347,7 @@
         <v>3</v>
       </c>
       <c r="E174" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.3">
@@ -3283,7 +3361,7 @@
         <v>2</v>
       </c>
       <c r="E175" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="176" spans="2:5" x14ac:dyDescent="0.3">
@@ -3297,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="E176" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="2:5" x14ac:dyDescent="0.3">
@@ -3311,7 +3389,7 @@
         <v>2</v>
       </c>
       <c r="E177" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="178" spans="2:5" x14ac:dyDescent="0.3">
@@ -3325,7 +3403,7 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="179" spans="2:5" x14ac:dyDescent="0.3">
@@ -3339,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="E179" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" spans="2:5" x14ac:dyDescent="0.3">
@@ -3353,7 +3431,7 @@
         <v>0</v>
       </c>
       <c r="E180" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="181" spans="2:5" x14ac:dyDescent="0.3">
@@ -3367,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="E181" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="182" spans="2:5" x14ac:dyDescent="0.3">
@@ -3381,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="E182" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="183" spans="2:5" x14ac:dyDescent="0.3">
@@ -3395,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="E183" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="184" spans="2:5" x14ac:dyDescent="0.3">
@@ -3409,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="E184" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="185" spans="2:5" x14ac:dyDescent="0.3">
@@ -3423,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="E185" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="186" spans="2:5" x14ac:dyDescent="0.3">
@@ -3437,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="E186" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" spans="2:5" x14ac:dyDescent="0.3">
@@ -3451,7 +3529,7 @@
         <v>1</v>
       </c>
       <c r="E187" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="2:5" x14ac:dyDescent="0.3">
@@ -3465,7 +3543,7 @@
         <v>1</v>
       </c>
       <c r="E188" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="2:5" x14ac:dyDescent="0.3">
@@ -3479,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="E189" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="2:5" x14ac:dyDescent="0.3">
@@ -3493,7 +3571,7 @@
         <v>1</v>
       </c>
       <c r="E190" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="2:5" x14ac:dyDescent="0.3">
@@ -3507,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="E191" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="2:5" x14ac:dyDescent="0.3">
@@ -3521,7 +3599,7 @@
         <v>0</v>
       </c>
       <c r="E192" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="193" spans="2:5" x14ac:dyDescent="0.3">
@@ -3535,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" spans="2:5" x14ac:dyDescent="0.3">
@@ -3549,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="E194" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="195" spans="2:5" x14ac:dyDescent="0.3">
@@ -3563,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="196" spans="2:5" x14ac:dyDescent="0.3">
@@ -3577,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="E196" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="197" spans="2:5" x14ac:dyDescent="0.3">
@@ -3591,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="E197" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="198" spans="2:5" x14ac:dyDescent="0.3">
@@ -3605,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="E198" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="199" spans="2:5" x14ac:dyDescent="0.3">
@@ -3619,7 +3697,7 @@
         <v>2</v>
       </c>
       <c r="E199" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200" spans="2:5" x14ac:dyDescent="0.3">
@@ -3633,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="201" spans="2:5" x14ac:dyDescent="0.3">
@@ -3647,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="E201" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="202" spans="2:5" x14ac:dyDescent="0.3">
@@ -3661,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="E202" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="203" spans="2:5" x14ac:dyDescent="0.3">
@@ -3675,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="E203" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="204" spans="2:5" x14ac:dyDescent="0.3">
@@ -3689,7 +3767,7 @@
         <v>0</v>
       </c>
       <c r="E204" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="205" spans="2:5" x14ac:dyDescent="0.3">
@@ -3703,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="E205" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="206" spans="2:5" x14ac:dyDescent="0.3">
@@ -3717,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="E206" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="207" spans="2:5" x14ac:dyDescent="0.3">
@@ -3731,7 +3809,7 @@
         <v>0</v>
       </c>
       <c r="E207" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="208" spans="2:5" x14ac:dyDescent="0.3">
@@ -3745,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="E208" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
     </row>
     <row r="209" spans="2:5" x14ac:dyDescent="0.3">
@@ -3759,7 +3837,7 @@
         <v>2</v>
       </c>
       <c r="E209" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="210" spans="2:5" x14ac:dyDescent="0.3">
@@ -3773,7 +3851,7 @@
         <v>2</v>
       </c>
       <c r="E210" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="211" spans="2:5" x14ac:dyDescent="0.3">
@@ -3787,7 +3865,7 @@
         <v>2</v>
       </c>
       <c r="E211" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.3">
@@ -3801,7 +3879,7 @@
         <v>1</v>
       </c>
       <c r="E212" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="213" spans="2:5" x14ac:dyDescent="0.3">
@@ -3815,7 +3893,7 @@
         <v>1</v>
       </c>
       <c r="E213" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.3">
@@ -3829,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="E214" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.3">
@@ -3843,7 +3921,7 @@
         <v>2</v>
       </c>
       <c r="E215" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="216" spans="2:5" x14ac:dyDescent="0.3">
@@ -3857,7 +3935,7 @@
         <v>2</v>
       </c>
       <c r="E216" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="217" spans="2:5" x14ac:dyDescent="0.3">
@@ -3871,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="E217" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="218" spans="2:5" x14ac:dyDescent="0.3">
@@ -3885,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="E218" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="219" spans="2:5" x14ac:dyDescent="0.3">
@@ -3899,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="E219" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="220" spans="2:5" x14ac:dyDescent="0.3">
@@ -3913,7 +3991,7 @@
         <v>0</v>
       </c>
       <c r="E220" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="221" spans="2:5" x14ac:dyDescent="0.3">
@@ -3927,7 +4005,7 @@
         <v>1</v>
       </c>
       <c r="E221" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="222" spans="2:5" x14ac:dyDescent="0.3">
@@ -3941,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="E222" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="223" spans="2:5" x14ac:dyDescent="0.3">
@@ -3955,7 +4033,7 @@
         <v>1</v>
       </c>
       <c r="E223" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="224" spans="2:5" x14ac:dyDescent="0.3">
@@ -3969,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="E224" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="225" spans="2:5" x14ac:dyDescent="0.3">
@@ -3983,7 +4061,7 @@
         <v>1</v>
       </c>
       <c r="E225" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="226" spans="2:5" x14ac:dyDescent="0.3">
@@ -3997,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="E226" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="227" spans="2:5" x14ac:dyDescent="0.3">
@@ -4011,7 +4089,7 @@
         <v>1</v>
       </c>
       <c r="E227" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.3">
@@ -4025,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="E228" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="229" spans="2:5" x14ac:dyDescent="0.3">
@@ -4039,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="E229" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="230" spans="2:5" x14ac:dyDescent="0.3">
@@ -4053,7 +4131,7 @@
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="231" spans="2:5" x14ac:dyDescent="0.3">
@@ -4067,7 +4145,7 @@
         <v>1</v>
       </c>
       <c r="E231" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="232" spans="2:5" x14ac:dyDescent="0.3">
@@ -4081,7 +4159,7 @@
         <v>0</v>
       </c>
       <c r="E232" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="233" spans="2:5" x14ac:dyDescent="0.3">
@@ -4095,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="E233" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="234" spans="2:5" x14ac:dyDescent="0.3">
@@ -4109,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="E234" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="235" spans="2:5" x14ac:dyDescent="0.3">
@@ -4123,7 +4201,7 @@
         <v>0</v>
       </c>
       <c r="E235" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="236" spans="2:5" x14ac:dyDescent="0.3">
@@ -4137,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="E236" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.3">
@@ -4151,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="E237" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="238" spans="2:5" x14ac:dyDescent="0.3">
@@ -4165,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="E238" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="239" spans="2:5" x14ac:dyDescent="0.3">
@@ -4179,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="E239" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="240" spans="2:5" x14ac:dyDescent="0.3">
@@ -4193,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="E240" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
     </row>
     <row r="241" spans="2:5" x14ac:dyDescent="0.3">
@@ -4207,7 +4285,7 @@
         <v>2</v>
       </c>
       <c r="E241" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="242" spans="2:5" x14ac:dyDescent="0.3">
@@ -4221,7 +4299,7 @@
         <v>2</v>
       </c>
       <c r="E242" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="243" spans="2:5" x14ac:dyDescent="0.3">
@@ -4235,7 +4313,7 @@
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.3">
@@ -4249,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="245" spans="2:5" x14ac:dyDescent="0.3">
@@ -4263,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="E245" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.3">
@@ -4277,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="E246" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.3">
@@ -4291,7 +4369,7 @@
         <v>1</v>
       </c>
       <c r="E247" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="248" spans="2:5" x14ac:dyDescent="0.3">
@@ -4305,7 +4383,7 @@
         <v>2</v>
       </c>
       <c r="E248" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="249" spans="2:5" x14ac:dyDescent="0.3">
@@ -4319,7 +4397,7 @@
         <v>2</v>
       </c>
       <c r="E249" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="250" spans="2:5" x14ac:dyDescent="0.3">
@@ -4333,7 +4411,7 @@
         <v>1</v>
       </c>
       <c r="E250" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="251" spans="2:5" x14ac:dyDescent="0.3">
@@ -4347,7 +4425,7 @@
         <v>1</v>
       </c>
       <c r="E251" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.3">
@@ -4361,7 +4439,7 @@
         <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="253" spans="2:5" x14ac:dyDescent="0.3">
@@ -4375,7 +4453,7 @@
         <v>2</v>
       </c>
       <c r="E253" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="254" spans="2:5" x14ac:dyDescent="0.3">
@@ -4389,7 +4467,7 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="255" spans="2:5" x14ac:dyDescent="0.3">
@@ -4403,7 +4481,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="256" spans="2:5" x14ac:dyDescent="0.3">
@@ -4417,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="E256" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="257" spans="2:5" x14ac:dyDescent="0.3">
@@ -4431,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="E257" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.3">
@@ -4445,7 +4523,7 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="259" spans="2:5" x14ac:dyDescent="0.3">
@@ -4459,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="E259" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="260" spans="2:5" x14ac:dyDescent="0.3">
@@ -4473,7 +4551,7 @@
         <v>2</v>
       </c>
       <c r="E260" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="261" spans="2:5" x14ac:dyDescent="0.3">
@@ -4487,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="E261" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="262" spans="2:5" x14ac:dyDescent="0.3">
@@ -4501,7 +4579,7 @@
         <v>1</v>
       </c>
       <c r="E262" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
     </row>
     <row r="263" spans="2:5" x14ac:dyDescent="0.3">
@@ -4515,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="E263" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="264" spans="2:5" x14ac:dyDescent="0.3">
@@ -4529,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="E264" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="265" spans="2:5" x14ac:dyDescent="0.3">
@@ -4543,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="E265" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="266" spans="2:5" x14ac:dyDescent="0.3">
@@ -4557,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="E266" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="267" spans="2:5" x14ac:dyDescent="0.3">
@@ -4571,7 +4649,7 @@
         <v>0</v>
       </c>
       <c r="E267" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="268" spans="2:5" x14ac:dyDescent="0.3">
@@ -4585,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="E268" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="269" spans="2:5" x14ac:dyDescent="0.3">
@@ -4599,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="E269" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="270" spans="2:5" x14ac:dyDescent="0.3">
@@ -4613,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="E270" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="271" spans="2:5" x14ac:dyDescent="0.3">
@@ -4627,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="E271" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="272" spans="2:5" x14ac:dyDescent="0.3">
@@ -4641,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="E272" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="273" spans="2:5" x14ac:dyDescent="0.3">
@@ -4655,7 +4733,7 @@
         <v>1</v>
       </c>
       <c r="E273" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="274" spans="2:5" x14ac:dyDescent="0.3">
@@ -4669,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="E274" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="275" spans="2:5" x14ac:dyDescent="0.3">
@@ -4683,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="E275" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="276" spans="2:5" x14ac:dyDescent="0.3">
@@ -4697,7 +4775,7 @@
         <v>1</v>
       </c>
       <c r="E276" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="277" spans="2:5" x14ac:dyDescent="0.3">
@@ -4711,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="E277" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="278" spans="2:5" x14ac:dyDescent="0.3">
@@ -4725,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="E278" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="279" spans="2:5" x14ac:dyDescent="0.3">
@@ -4739,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="E279" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="280" spans="2:5" x14ac:dyDescent="0.3">
@@ -4753,7 +4831,7 @@
         <v>1</v>
       </c>
       <c r="E280" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="281" spans="2:5" x14ac:dyDescent="0.3">
@@ -4767,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="E281" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="282" spans="2:5" x14ac:dyDescent="0.3">
@@ -4781,7 +4859,7 @@
         <v>0</v>
       </c>
       <c r="E282" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="283" spans="2:5" x14ac:dyDescent="0.3">
@@ -4795,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="E283" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="284" spans="2:5" x14ac:dyDescent="0.3">
@@ -4809,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="E284" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="285" spans="2:5" x14ac:dyDescent="0.3">
@@ -4823,7 +4901,7 @@
         <v>2</v>
       </c>
       <c r="E285" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="286" spans="2:5" x14ac:dyDescent="0.3">
@@ -4837,7 +4915,7 @@
         <v>2</v>
       </c>
       <c r="E286" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="287" spans="2:5" x14ac:dyDescent="0.3">
@@ -4851,7 +4929,7 @@
         <v>2</v>
       </c>
       <c r="E287" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="288" spans="2:5" x14ac:dyDescent="0.3">
@@ -4865,7 +4943,7 @@
         <v>2</v>
       </c>
       <c r="E288" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="289" spans="2:5" x14ac:dyDescent="0.3">
@@ -4879,7 +4957,7 @@
         <v>2</v>
       </c>
       <c r="E289" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="290" spans="2:5" x14ac:dyDescent="0.3">
@@ -4893,7 +4971,7 @@
         <v>3</v>
       </c>
       <c r="E290" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="291" spans="2:5" x14ac:dyDescent="0.3">
@@ -4907,7 +4985,7 @@
         <v>2</v>
       </c>
       <c r="E291" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="292" spans="2:5" x14ac:dyDescent="0.3">
@@ -4921,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="E292" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="293" spans="2:5" x14ac:dyDescent="0.3">
@@ -4935,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="E293" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="294" spans="2:5" x14ac:dyDescent="0.3">
@@ -4949,7 +5027,7 @@
         <v>2</v>
       </c>
       <c r="E294" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="295" spans="2:5" x14ac:dyDescent="0.3">
@@ -4963,7 +5041,7 @@
         <v>2</v>
       </c>
       <c r="E295" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
     </row>
     <row r="296" spans="2:5" x14ac:dyDescent="0.3">
@@ -4977,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="E296" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="297" spans="2:5" x14ac:dyDescent="0.3">
@@ -4991,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="E297" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="298" spans="2:5" x14ac:dyDescent="0.3">
@@ -5005,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="E298" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="299" spans="2:5" x14ac:dyDescent="0.3">
@@ -5019,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="E299" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="300" spans="2:5" x14ac:dyDescent="0.3">
@@ -5033,7 +5111,7 @@
         <v>2</v>
       </c>
       <c r="E300" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="301" spans="2:5" x14ac:dyDescent="0.3">
@@ -5047,7 +5125,7 @@
         <v>1</v>
       </c>
       <c r="E301" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="302" spans="2:5" x14ac:dyDescent="0.3">
@@ -5061,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="E302" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="303" spans="2:5" x14ac:dyDescent="0.3">
@@ -5075,7 +5153,7 @@
         <v>1</v>
       </c>
       <c r="E303" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="304" spans="2:5" x14ac:dyDescent="0.3">
@@ -5089,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="E304" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="305" spans="2:5" x14ac:dyDescent="0.3">
@@ -5103,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="E305" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="306" spans="2:5" x14ac:dyDescent="0.3">
@@ -5117,7 +5195,7 @@
         <v>0</v>
       </c>
       <c r="E306" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="307" spans="2:5" x14ac:dyDescent="0.3">
@@ -5131,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="E307" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="308" spans="2:5" x14ac:dyDescent="0.3">
@@ -5145,7 +5223,7 @@
         <v>2</v>
       </c>
       <c r="E308" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="309" spans="2:5" x14ac:dyDescent="0.3">
@@ -5159,7 +5237,7 @@
         <v>1</v>
       </c>
       <c r="E309" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="310" spans="2:5" x14ac:dyDescent="0.3">
@@ -5173,7 +5251,7 @@
         <v>3</v>
       </c>
       <c r="E310" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="311" spans="2:5" x14ac:dyDescent="0.3">
@@ -5187,7 +5265,7 @@
         <v>2</v>
       </c>
       <c r="E311" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="312" spans="2:5" x14ac:dyDescent="0.3">
@@ -5201,7 +5279,7 @@
         <v>1</v>
       </c>
       <c r="E312" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="313" spans="2:5" x14ac:dyDescent="0.3">
@@ -5215,7 +5293,7 @@
         <v>2</v>
       </c>
       <c r="E313" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="314" spans="2:5" x14ac:dyDescent="0.3">
@@ -5229,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="E314" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="315" spans="2:5" x14ac:dyDescent="0.3">
@@ -5243,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="E315" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="316" spans="2:5" x14ac:dyDescent="0.3">
@@ -5257,7 +5335,7 @@
         <v>2</v>
       </c>
       <c r="E316" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="317" spans="2:5" x14ac:dyDescent="0.3">
@@ -5271,7 +5349,7 @@
         <v>2</v>
       </c>
       <c r="E317" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="318" spans="2:5" x14ac:dyDescent="0.3">
@@ -5285,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="E318" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="319" spans="2:5" x14ac:dyDescent="0.3">
@@ -5299,7 +5377,7 @@
         <v>0</v>
       </c>
       <c r="E319" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="320" spans="2:5" x14ac:dyDescent="0.3">
@@ -5313,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="E320" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="321" spans="2:5" x14ac:dyDescent="0.3">
@@ -5327,7 +5405,7 @@
         <v>1</v>
       </c>
       <c r="E321" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="322" spans="2:5" x14ac:dyDescent="0.3">
@@ -5341,7 +5419,7 @@
         <v>1</v>
       </c>
       <c r="E322" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="323" spans="2:5" x14ac:dyDescent="0.3">
@@ -5355,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="E323" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="324" spans="2:5" x14ac:dyDescent="0.3">
@@ -5369,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="E324" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="325" spans="2:5" x14ac:dyDescent="0.3">
@@ -5383,7 +5461,7 @@
         <v>1</v>
       </c>
       <c r="E325" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="326" spans="2:5" x14ac:dyDescent="0.3">
@@ -5397,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="E326" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="327" spans="2:5" x14ac:dyDescent="0.3">
@@ -5411,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="E327" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="328" spans="2:5" x14ac:dyDescent="0.3">
@@ -5425,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="E328" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
     </row>
     <row r="329" spans="2:5" x14ac:dyDescent="0.3">
@@ -5439,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="E329" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="330" spans="2:5" x14ac:dyDescent="0.3">
@@ -5453,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="E330" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="331" spans="2:5" x14ac:dyDescent="0.3">
@@ -5467,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="E331" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="332" spans="2:5" x14ac:dyDescent="0.3">
@@ -5481,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="E332" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="333" spans="2:5" x14ac:dyDescent="0.3">
@@ -5495,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="E333" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="334" spans="2:5" x14ac:dyDescent="0.3">
@@ -5509,7 +5587,7 @@
         <v>0</v>
       </c>
       <c r="E334" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="335" spans="2:5" x14ac:dyDescent="0.3">
@@ -5523,7 +5601,7 @@
         <v>0</v>
       </c>
       <c r="E335" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="336" spans="2:5" x14ac:dyDescent="0.3">
@@ -5537,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="E336" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="337" spans="2:5" x14ac:dyDescent="0.3">
@@ -5551,7 +5629,7 @@
         <v>0</v>
       </c>
       <c r="E337" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="338" spans="2:5" x14ac:dyDescent="0.3">
@@ -5565,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="E338" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="339" spans="2:5" x14ac:dyDescent="0.3">
@@ -5579,7 +5657,7 @@
         <v>1</v>
       </c>
       <c r="E339" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="340" spans="2:5" x14ac:dyDescent="0.3">
@@ -5593,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="E340" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
     </row>
     <row r="341" spans="2:5" x14ac:dyDescent="0.3">
@@ -5607,7 +5685,7 @@
         <v>2</v>
       </c>
       <c r="E341" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="342" spans="2:5" x14ac:dyDescent="0.3">
@@ -5621,7 +5699,7 @@
         <v>2</v>
       </c>
       <c r="E342" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="343" spans="2:5" x14ac:dyDescent="0.3">
@@ -5635,7 +5713,7 @@
         <v>1</v>
       </c>
       <c r="E343" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="344" spans="2:5" x14ac:dyDescent="0.3">
@@ -5649,7 +5727,7 @@
         <v>3</v>
       </c>
       <c r="E344" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="345" spans="2:5" x14ac:dyDescent="0.3">
@@ -5663,7 +5741,7 @@
         <v>3</v>
       </c>
       <c r="E345" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="346" spans="2:5" x14ac:dyDescent="0.3">
@@ -5677,7 +5755,7 @@
         <v>2</v>
       </c>
       <c r="E346" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="347" spans="2:5" x14ac:dyDescent="0.3">
@@ -5691,7 +5769,7 @@
         <v>2</v>
       </c>
       <c r="E347" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="348" spans="2:5" x14ac:dyDescent="0.3">
@@ -5705,7 +5783,7 @@
         <v>3</v>
       </c>
       <c r="E348" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="349" spans="2:5" x14ac:dyDescent="0.3">
@@ -5719,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="E349" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="350" spans="2:5" x14ac:dyDescent="0.3">
@@ -5733,7 +5811,7 @@
         <v>1</v>
       </c>
       <c r="E350" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="351" spans="2:5" x14ac:dyDescent="0.3">
@@ -5747,7 +5825,7 @@
         <v>2</v>
       </c>
       <c r="E351" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="352" spans="2:5" x14ac:dyDescent="0.3">
@@ -5761,7 +5839,7 @@
         <v>3</v>
       </c>
       <c r="E352" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
     </row>
     <row r="353" spans="2:5" x14ac:dyDescent="0.3">
@@ -5775,7 +5853,7 @@
         <v>2</v>
       </c>
       <c r="E353" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="354" spans="2:5" x14ac:dyDescent="0.3">
@@ -5789,7 +5867,7 @@
         <v>2</v>
       </c>
       <c r="E354" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="355" spans="2:5" x14ac:dyDescent="0.3">
@@ -5803,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="E355" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="356" spans="2:5" x14ac:dyDescent="0.3">
@@ -5817,7 +5895,7 @@
         <v>2</v>
       </c>
       <c r="E356" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="357" spans="2:5" x14ac:dyDescent="0.3">
@@ -5831,7 +5909,7 @@
         <v>2</v>
       </c>
       <c r="E357" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="358" spans="2:5" x14ac:dyDescent="0.3">
@@ -5845,7 +5923,7 @@
         <v>2</v>
       </c>
       <c r="E358" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="359" spans="2:5" x14ac:dyDescent="0.3">
@@ -5859,7 +5937,7 @@
         <v>2</v>
       </c>
       <c r="E359" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="360" spans="2:5" x14ac:dyDescent="0.3">
@@ -5873,7 +5951,7 @@
         <v>1</v>
       </c>
       <c r="E360" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="361" spans="2:5" x14ac:dyDescent="0.3">
@@ -5887,7 +5965,7 @@
         <v>2</v>
       </c>
       <c r="E361" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="362" spans="2:5" x14ac:dyDescent="0.3">
@@ -5901,7 +5979,7 @@
         <v>3</v>
       </c>
       <c r="E362" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="363" spans="2:5" x14ac:dyDescent="0.3">
@@ -5915,7 +5993,7 @@
         <v>3</v>
       </c>
       <c r="E363" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="364" spans="2:5" x14ac:dyDescent="0.3">
@@ -5929,7 +6007,7 @@
         <v>2</v>
       </c>
       <c r="E364" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="365" spans="2:5" x14ac:dyDescent="0.3">
@@ -5943,7 +6021,7 @@
         <v>2</v>
       </c>
       <c r="E365" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="366" spans="2:5" x14ac:dyDescent="0.3">
@@ -5957,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="E366" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="367" spans="2:5" x14ac:dyDescent="0.3">
@@ -5971,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="E367" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="368" spans="2:5" x14ac:dyDescent="0.3">
@@ -5985,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="E368" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="369" spans="2:5" x14ac:dyDescent="0.3">
@@ -5999,7 +6077,7 @@
         <v>2</v>
       </c>
       <c r="E369" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="370" spans="2:5" x14ac:dyDescent="0.3">
@@ -6013,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="E370" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="371" spans="2:5" x14ac:dyDescent="0.3">
@@ -6027,7 +6105,7 @@
         <v>1</v>
       </c>
       <c r="E371" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="372" spans="2:5" x14ac:dyDescent="0.3">
@@ -6041,7 +6119,7 @@
         <v>3</v>
       </c>
       <c r="E372" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="373" spans="2:5" x14ac:dyDescent="0.3">
@@ -6055,7 +6133,7 @@
         <v>2</v>
       </c>
       <c r="E373" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="374" spans="2:5" x14ac:dyDescent="0.3">
@@ -6069,7 +6147,7 @@
         <v>2</v>
       </c>
       <c r="E374" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="375" spans="2:5" x14ac:dyDescent="0.3">
@@ -6083,7 +6161,7 @@
         <v>1</v>
       </c>
       <c r="E375" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
     <row r="376" spans="2:5" x14ac:dyDescent="0.3">
@@ -6097,7 +6175,7 @@
         <v>2</v>
       </c>
       <c r="E376" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="377" spans="2:5" x14ac:dyDescent="0.3">
@@ -6111,7 +6189,7 @@
         <v>3</v>
       </c>
       <c r="E377" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="378" spans="2:5" x14ac:dyDescent="0.3">
@@ -6125,7 +6203,7 @@
         <v>4</v>
       </c>
       <c r="E378" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="379" spans="2:5" x14ac:dyDescent="0.3">
@@ -6139,7 +6217,7 @@
         <v>4</v>
       </c>
       <c r="E379" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="380" spans="2:5" x14ac:dyDescent="0.3">
@@ -6153,7 +6231,7 @@
         <v>3</v>
       </c>
       <c r="E380" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="381" spans="2:5" x14ac:dyDescent="0.3">
@@ -6167,7 +6245,7 @@
         <v>3</v>
       </c>
       <c r="E381" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="382" spans="2:5" x14ac:dyDescent="0.3">
@@ -6181,7 +6259,7 @@
         <v>2</v>
       </c>
       <c r="E382" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="383" spans="2:5" x14ac:dyDescent="0.3">
@@ -6195,7 +6273,7 @@
         <v>3</v>
       </c>
       <c r="E383" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="384" spans="2:5" x14ac:dyDescent="0.3">
@@ -6209,7 +6287,7 @@
         <v>3</v>
       </c>
       <c r="E384" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="385" spans="2:5" x14ac:dyDescent="0.3">
@@ -6223,7 +6301,7 @@
         <v>3</v>
       </c>
       <c r="E385" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="386" spans="2:5" x14ac:dyDescent="0.3">
@@ -6237,7 +6315,7 @@
         <v>2</v>
       </c>
       <c r="E386" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="387" spans="2:5" x14ac:dyDescent="0.3">
@@ -6251,7 +6329,7 @@
         <v>2</v>
       </c>
       <c r="E387" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="388" spans="2:5" x14ac:dyDescent="0.3">
@@ -6265,7 +6343,7 @@
         <v>2</v>
       </c>
       <c r="E388" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="389" spans="2:5" x14ac:dyDescent="0.3">
@@ -6279,7 +6357,7 @@
         <v>2</v>
       </c>
       <c r="E389" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="390" spans="2:5" x14ac:dyDescent="0.3">
@@ -6293,7 +6371,7 @@
         <v>3</v>
       </c>
       <c r="E390" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="391" spans="2:5" x14ac:dyDescent="0.3">
@@ -6307,7 +6385,7 @@
         <v>2</v>
       </c>
       <c r="E391" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="392" spans="2:5" x14ac:dyDescent="0.3">
@@ -6321,7 +6399,7 @@
         <v>2</v>
       </c>
       <c r="E392" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="393" spans="2:5" x14ac:dyDescent="0.3">
@@ -6335,7 +6413,7 @@
         <v>3</v>
       </c>
       <c r="E393" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="394" spans="2:5" x14ac:dyDescent="0.3">
@@ -6349,7 +6427,7 @@
         <v>2</v>
       </c>
       <c r="E394" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="395" spans="2:5" x14ac:dyDescent="0.3">
@@ -6363,7 +6441,7 @@
         <v>3</v>
       </c>
       <c r="E395" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="396" spans="2:5" x14ac:dyDescent="0.3">
@@ -6377,7 +6455,7 @@
         <v>3</v>
       </c>
       <c r="E396" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="397" spans="2:5" x14ac:dyDescent="0.3">
@@ -6391,7 +6469,7 @@
         <v>2</v>
       </c>
       <c r="E397" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="398" spans="2:5" x14ac:dyDescent="0.3">
@@ -6405,7 +6483,7 @@
         <v>2</v>
       </c>
       <c r="E398" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="399" spans="2:5" x14ac:dyDescent="0.3">
@@ -6419,7 +6497,7 @@
         <v>2</v>
       </c>
       <c r="E399" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="400" spans="2:5" x14ac:dyDescent="0.3">
@@ -6433,7 +6511,7 @@
         <v>2</v>
       </c>
       <c r="E400" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="401" spans="2:5" x14ac:dyDescent="0.3">
@@ -6447,7 +6525,7 @@
         <v>6</v>
       </c>
       <c r="E401" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="402" spans="2:5" x14ac:dyDescent="0.3">
@@ -6461,7 +6539,7 @@
         <v>2</v>
       </c>
       <c r="E402" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="403" spans="2:5" x14ac:dyDescent="0.3">
@@ -6475,7 +6553,7 @@
         <v>3</v>
       </c>
       <c r="E403" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="404" spans="2:5" x14ac:dyDescent="0.3">
@@ -6489,7 +6567,7 @@
         <v>2</v>
       </c>
       <c r="E404" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="405" spans="2:5" x14ac:dyDescent="0.3">
@@ -6503,7 +6581,7 @@
         <v>3</v>
       </c>
       <c r="E405" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="406" spans="2:5" x14ac:dyDescent="0.3">
@@ -6517,7 +6595,7 @@
         <v>4</v>
       </c>
       <c r="E406" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="407" spans="2:5" x14ac:dyDescent="0.3">
@@ -6531,7 +6609,7 @@
         <v>4</v>
       </c>
       <c r="E407" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="408" spans="2:5" x14ac:dyDescent="0.3">
@@ -6545,7 +6623,7 @@
         <v>3</v>
       </c>
       <c r="E408" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="409" spans="2:5" x14ac:dyDescent="0.3">
@@ -6559,7 +6637,7 @@
         <v>2</v>
       </c>
       <c r="E409" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="410" spans="2:5" x14ac:dyDescent="0.3">
@@ -6573,7 +6651,7 @@
         <v>4</v>
       </c>
       <c r="E410" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="411" spans="2:5" x14ac:dyDescent="0.3">
@@ -6587,7 +6665,7 @@
         <v>1</v>
       </c>
       <c r="E411" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="412" spans="2:5" x14ac:dyDescent="0.3">
@@ -6601,7 +6679,7 @@
         <v>1</v>
       </c>
       <c r="E412" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="413" spans="2:5" x14ac:dyDescent="0.3">
@@ -6615,7 +6693,7 @@
         <v>1</v>
       </c>
       <c r="E413" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="414" spans="2:5" x14ac:dyDescent="0.3">
@@ -6629,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="E414" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="415" spans="2:5" x14ac:dyDescent="0.3">
@@ -6643,7 +6721,7 @@
         <v>1</v>
       </c>
       <c r="E415" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="416" spans="2:5" x14ac:dyDescent="0.3">
@@ -6657,7 +6735,7 @@
         <v>0</v>
       </c>
       <c r="E416" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="417" spans="2:5" x14ac:dyDescent="0.3">
@@ -6671,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="E417" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="418" spans="2:5" x14ac:dyDescent="0.3">
@@ -6685,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="E418" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="419" spans="2:5" x14ac:dyDescent="0.3">
@@ -6699,7 +6777,7 @@
         <v>1</v>
       </c>
       <c r="E419" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="420" spans="2:5" x14ac:dyDescent="0.3">
@@ -6713,7 +6791,7 @@
         <v>1</v>
       </c>
       <c r="E420" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="421" spans="2:5" x14ac:dyDescent="0.3">
@@ -6727,7 +6805,7 @@
         <v>1</v>
       </c>
       <c r="E421" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="422" spans="2:5" x14ac:dyDescent="0.3">
@@ -6741,7 +6819,7 @@
         <v>2</v>
       </c>
       <c r="E422" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="423" spans="2:5" x14ac:dyDescent="0.3">
@@ -6755,7 +6833,7 @@
         <v>2</v>
       </c>
       <c r="E423" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="424" spans="2:5" x14ac:dyDescent="0.3">
@@ -6769,7 +6847,7 @@
         <v>2</v>
       </c>
       <c r="E424" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="425" spans="2:5" x14ac:dyDescent="0.3">
@@ -6783,7 +6861,7 @@
         <v>3</v>
       </c>
       <c r="E425" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="426" spans="2:5" x14ac:dyDescent="0.3">
@@ -6797,7 +6875,7 @@
         <v>2</v>
       </c>
       <c r="E426" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="427" spans="2:5" x14ac:dyDescent="0.3">
@@ -6811,7 +6889,7 @@
         <v>3</v>
       </c>
       <c r="E427" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="428" spans="2:5" x14ac:dyDescent="0.3">
@@ -6825,7 +6903,7 @@
         <v>3</v>
       </c>
       <c r="E428" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="429" spans="2:5" x14ac:dyDescent="0.3">
@@ -6839,7 +6917,7 @@
         <v>2</v>
       </c>
       <c r="E429" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="430" spans="2:5" x14ac:dyDescent="0.3">
@@ -6853,7 +6931,7 @@
         <v>2</v>
       </c>
       <c r="E430" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="431" spans="2:5" x14ac:dyDescent="0.3">
@@ -6867,7 +6945,7 @@
         <v>4</v>
       </c>
       <c r="E431" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="432" spans="2:5" x14ac:dyDescent="0.3">
@@ -6881,7 +6959,7 @@
         <v>3</v>
       </c>
       <c r="E432" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="433" spans="2:5" x14ac:dyDescent="0.3">
@@ -6895,7 +6973,7 @@
         <v>2</v>
       </c>
       <c r="E433" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="434" spans="2:5" x14ac:dyDescent="0.3">
@@ -6909,7 +6987,7 @@
         <v>2</v>
       </c>
       <c r="E434" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="435" spans="2:5" x14ac:dyDescent="0.3">
@@ -6923,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="E435" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="436" spans="2:5" x14ac:dyDescent="0.3">
@@ -6937,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="E436" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="437" spans="2:5" x14ac:dyDescent="0.3">
@@ -6951,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="E437" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="438" spans="2:5" x14ac:dyDescent="0.3">
@@ -6965,7 +7043,7 @@
         <v>2</v>
       </c>
       <c r="E438" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="439" spans="2:5" x14ac:dyDescent="0.3">
@@ -6979,7 +7057,7 @@
         <v>1</v>
       </c>
       <c r="E439" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="440" spans="2:5" x14ac:dyDescent="0.3">
@@ -6993,7 +7071,7 @@
         <v>2</v>
       </c>
       <c r="E440" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="441" spans="2:5" x14ac:dyDescent="0.3">
@@ -7007,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="E441" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="442" spans="2:5" x14ac:dyDescent="0.3">
@@ -7021,7 +7099,7 @@
         <v>1</v>
       </c>
       <c r="E442" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="443" spans="2:5" x14ac:dyDescent="0.3">
@@ -7035,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="E443" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="444" spans="2:5" x14ac:dyDescent="0.3">
@@ -7049,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="E444" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="445" spans="2:5" x14ac:dyDescent="0.3">
@@ -7063,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="E445" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="446" spans="2:5" x14ac:dyDescent="0.3">
@@ -7077,7 +7155,7 @@
         <v>2</v>
       </c>
       <c r="E446" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="447" spans="2:5" x14ac:dyDescent="0.3">
@@ -7091,7 +7169,7 @@
         <v>3</v>
       </c>
       <c r="E447" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="448" spans="2:5" x14ac:dyDescent="0.3">
@@ -7105,7 +7183,7 @@
         <v>3</v>
       </c>
       <c r="E448" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="449" spans="2:5" x14ac:dyDescent="0.3">
@@ -7119,7 +7197,7 @@
         <v>2</v>
       </c>
       <c r="E449" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="450" spans="2:5" x14ac:dyDescent="0.3">
@@ -7133,7 +7211,7 @@
         <v>2</v>
       </c>
       <c r="E450" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="451" spans="2:5" x14ac:dyDescent="0.3">
@@ -7147,7 +7225,7 @@
         <v>3</v>
       </c>
       <c r="E451" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="452" spans="2:5" x14ac:dyDescent="0.3">
@@ -7161,7 +7239,7 @@
         <v>3</v>
       </c>
       <c r="E452" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="453" spans="2:5" x14ac:dyDescent="0.3">
@@ -7175,7 +7253,7 @@
         <v>4</v>
       </c>
       <c r="E453" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="454" spans="2:5" x14ac:dyDescent="0.3">
@@ -7189,7 +7267,7 @@
         <v>3</v>
       </c>
       <c r="E454" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="455" spans="2:5" x14ac:dyDescent="0.3">
@@ -7203,7 +7281,7 @@
         <v>3</v>
       </c>
       <c r="E455" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="456" spans="2:5" x14ac:dyDescent="0.3">
@@ -7217,7 +7295,7 @@
         <v>2</v>
       </c>
       <c r="E456" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
     </row>
     <row r="457" spans="2:5" x14ac:dyDescent="0.3">
@@ -7231,6 +7309,3847 @@
         <v>3</v>
       </c>
       <c r="E457" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="458" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B458" t="s">
+        <v>14</v>
+      </c>
+      <c r="C458">
+        <v>2</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+      <c r="E458" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="459" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B459" t="s">
+        <v>13</v>
+      </c>
+      <c r="C459">
+        <v>2</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+      <c r="E459" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="460" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B460" t="s">
+        <v>9</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+      <c r="E460" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="461" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B461" t="s">
+        <v>8</v>
+      </c>
+      <c r="C461">
+        <v>3</v>
+      </c>
+      <c r="D461">
+        <v>1</v>
+      </c>
+      <c r="E461" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="462" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B462" t="s">
+        <v>16</v>
+      </c>
+      <c r="C462">
+        <v>2</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+      <c r="E462" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="463" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B463" t="s">
+        <v>11</v>
+      </c>
+      <c r="C463">
+        <v>2</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+      <c r="E463" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="464" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B464" t="s">
+        <v>6</v>
+      </c>
+      <c r="C464">
+        <v>2</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+      <c r="E464" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="465" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B465" t="s">
+        <v>15</v>
+      </c>
+      <c r="C465">
+        <v>2</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+      <c r="E465" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="466" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B466" t="s">
+        <v>7</v>
+      </c>
+      <c r="C466">
+        <v>2</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+      <c r="E466" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="467" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B467" t="s">
+        <v>12</v>
+      </c>
+      <c r="C467">
+        <v>2</v>
+      </c>
+      <c r="D467">
+        <v>1</v>
+      </c>
+      <c r="E467" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="468" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B468" t="s">
+        <v>5</v>
+      </c>
+      <c r="C468">
+        <v>2</v>
+      </c>
+      <c r="D468">
+        <v>1</v>
+      </c>
+      <c r="E468" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="469" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B469" t="s">
+        <v>14</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469">
+        <v>2</v>
+      </c>
+      <c r="E469" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="470" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B470" t="s">
+        <v>13</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470">
+        <v>2</v>
+      </c>
+      <c r="E470" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="471" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B471" t="s">
+        <v>9</v>
+      </c>
+      <c r="C471">
+        <v>0</v>
+      </c>
+      <c r="D471">
+        <v>2</v>
+      </c>
+      <c r="E471" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="472" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B472" t="s">
+        <v>8</v>
+      </c>
+      <c r="C472">
+        <v>0</v>
+      </c>
+      <c r="D472">
+        <v>3</v>
+      </c>
+      <c r="E472" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="473" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B473" t="s">
+        <v>16</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473">
+        <v>1</v>
+      </c>
+      <c r="E473" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="474" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B474" t="s">
+        <v>11</v>
+      </c>
+      <c r="C474">
+        <v>0</v>
+      </c>
+      <c r="D474">
+        <v>1</v>
+      </c>
+      <c r="E474" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="475" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B475" t="s">
+        <v>6</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+      <c r="D475">
+        <v>2</v>
+      </c>
+      <c r="E475" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="476" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B476" t="s">
+        <v>15</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+      <c r="D476">
+        <v>2</v>
+      </c>
+      <c r="E476" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="477" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B477" t="s">
+        <v>7</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+      <c r="D477">
+        <v>2</v>
+      </c>
+      <c r="E477" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="478" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B478" t="s">
+        <v>12</v>
+      </c>
+      <c r="C478">
+        <v>1</v>
+      </c>
+      <c r="D478">
+        <v>2</v>
+      </c>
+      <c r="E478" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="479" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B479" t="s">
+        <v>5</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+      <c r="D479">
+        <v>2</v>
+      </c>
+      <c r="E479" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="480" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B480" t="s">
+        <v>14</v>
+      </c>
+      <c r="C480">
+        <v>2</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+      <c r="E480" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="481" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B481" t="s">
+        <v>13</v>
+      </c>
+      <c r="C481">
+        <v>1</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+      <c r="E481" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="482" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B482" t="s">
+        <v>9</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482">
+        <v>0</v>
+      </c>
+      <c r="E482" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="483" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B483" t="s">
+        <v>8</v>
+      </c>
+      <c r="C483">
+        <v>2</v>
+      </c>
+      <c r="D483">
+        <v>0</v>
+      </c>
+      <c r="E483" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="484" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B484" t="s">
+        <v>16</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+      <c r="D484">
+        <v>2</v>
+      </c>
+      <c r="E484" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="485" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B485" t="s">
+        <v>6</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485">
+        <v>1</v>
+      </c>
+      <c r="E485" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="486" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B486" t="s">
+        <v>15</v>
+      </c>
+      <c r="C486">
+        <v>1</v>
+      </c>
+      <c r="D486">
+        <v>0</v>
+      </c>
+      <c r="E486" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="487" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B487" t="s">
+        <v>7</v>
+      </c>
+      <c r="C487">
+        <v>1</v>
+      </c>
+      <c r="D487">
+        <v>0</v>
+      </c>
+      <c r="E487" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="488" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B488" t="s">
+        <v>12</v>
+      </c>
+      <c r="C488">
+        <v>1</v>
+      </c>
+      <c r="D488">
+        <v>0</v>
+      </c>
+      <c r="E488" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="489" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B489" t="s">
+        <v>11</v>
+      </c>
+      <c r="C489">
+        <v>1</v>
+      </c>
+      <c r="D489">
+        <v>0</v>
+      </c>
+      <c r="E489" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="490" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B490" t="s">
+        <v>5</v>
+      </c>
+      <c r="C490">
+        <v>1</v>
+      </c>
+      <c r="D490">
+        <v>0</v>
+      </c>
+      <c r="E490" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="491" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B491" t="s">
+        <v>14</v>
+      </c>
+      <c r="C491">
+        <v>0</v>
+      </c>
+      <c r="D491">
+        <v>2</v>
+      </c>
+      <c r="E491" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="492" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B492" t="s">
+        <v>13</v>
+      </c>
+      <c r="C492">
+        <v>0</v>
+      </c>
+      <c r="D492">
+        <v>1</v>
+      </c>
+      <c r="E492" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="493" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B493" t="s">
+        <v>9</v>
+      </c>
+      <c r="C493">
+        <v>0</v>
+      </c>
+      <c r="D493">
+        <v>3</v>
+      </c>
+      <c r="E493" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="494" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B494" t="s">
+        <v>8</v>
+      </c>
+      <c r="C494">
+        <v>1</v>
+      </c>
+      <c r="D494">
+        <v>2</v>
+      </c>
+      <c r="E494" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="495" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B495" t="s">
+        <v>15</v>
+      </c>
+      <c r="C495">
+        <v>0</v>
+      </c>
+      <c r="D495">
+        <v>2</v>
+      </c>
+      <c r="E495" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="496" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B496" t="s">
+        <v>7</v>
+      </c>
+      <c r="C496">
+        <v>0</v>
+      </c>
+      <c r="D496">
+        <v>2</v>
+      </c>
+      <c r="E496" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="497" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B497" t="s">
+        <v>12</v>
+      </c>
+      <c r="C497">
+        <v>0</v>
+      </c>
+      <c r="D497">
+        <v>1</v>
+      </c>
+      <c r="E497" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="498" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B498" t="s">
+        <v>11</v>
+      </c>
+      <c r="C498">
+        <v>0</v>
+      </c>
+      <c r="D498">
+        <v>2</v>
+      </c>
+      <c r="E498" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="499" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B499" t="s">
+        <v>6</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+      <c r="D499">
+        <v>2</v>
+      </c>
+      <c r="E499" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="500" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B500" t="s">
+        <v>5</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500">
+        <v>3</v>
+      </c>
+      <c r="E500" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="501" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B501" t="s">
+        <v>14</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+      <c r="D501">
+        <v>1</v>
+      </c>
+      <c r="E501" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="502" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B502" t="s">
+        <v>13</v>
+      </c>
+      <c r="C502">
+        <v>2</v>
+      </c>
+      <c r="D502">
+        <v>0</v>
+      </c>
+      <c r="E502" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="503" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B503" t="s">
+        <v>9</v>
+      </c>
+      <c r="C503">
+        <v>0</v>
+      </c>
+      <c r="D503">
+        <v>0</v>
+      </c>
+      <c r="E503" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="504" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B504" t="s">
+        <v>8</v>
+      </c>
+      <c r="C504">
+        <v>2</v>
+      </c>
+      <c r="D504">
+        <v>0</v>
+      </c>
+      <c r="E504" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="505" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B505" t="s">
+        <v>15</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+      <c r="D505">
+        <v>0</v>
+      </c>
+      <c r="E505" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="506" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B506" t="s">
+        <v>7</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+      <c r="D506">
+        <v>0</v>
+      </c>
+      <c r="E506" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="507" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B507" t="s">
+        <v>12</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+      <c r="D507">
+        <v>0</v>
+      </c>
+      <c r="E507" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="508" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B508" t="s">
+        <v>11</v>
+      </c>
+      <c r="C508">
+        <v>2</v>
+      </c>
+      <c r="D508">
+        <v>1</v>
+      </c>
+      <c r="E508" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="509" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B509" t="s">
+        <v>6</v>
+      </c>
+      <c r="C509">
+        <v>3</v>
+      </c>
+      <c r="D509">
+        <v>1</v>
+      </c>
+      <c r="E509" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="510" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B510" t="s">
+        <v>5</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510">
+        <v>1</v>
+      </c>
+      <c r="E510" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="511" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B511" t="s">
+        <v>14</v>
+      </c>
+      <c r="C511">
+        <v>0</v>
+      </c>
+      <c r="D511">
+        <v>2</v>
+      </c>
+      <c r="E511" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="512" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B512" t="s">
+        <v>13</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512">
+        <v>4</v>
+      </c>
+      <c r="E512" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="513" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B513" t="s">
+        <v>9</v>
+      </c>
+      <c r="C513">
+        <v>0</v>
+      </c>
+      <c r="D513">
+        <v>2</v>
+      </c>
+      <c r="E513" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="514" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B514" t="s">
+        <v>8</v>
+      </c>
+      <c r="C514">
+        <v>0</v>
+      </c>
+      <c r="D514">
+        <v>2</v>
+      </c>
+      <c r="E514" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="515" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B515" t="s">
+        <v>11</v>
+      </c>
+      <c r="C515">
+        <v>0</v>
+      </c>
+      <c r="D515">
+        <v>3</v>
+      </c>
+      <c r="E515" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="516" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B516" t="s">
+        <v>7</v>
+      </c>
+      <c r="C516">
+        <v>0</v>
+      </c>
+      <c r="D516">
+        <v>2</v>
+      </c>
+      <c r="E516" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="517" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B517" t="s">
+        <v>15</v>
+      </c>
+      <c r="C517">
+        <v>0</v>
+      </c>
+      <c r="D517">
+        <v>2</v>
+      </c>
+      <c r="E517" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="518" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B518" t="s">
+        <v>6</v>
+      </c>
+      <c r="C518">
+        <v>0</v>
+      </c>
+      <c r="D518">
+        <v>2</v>
+      </c>
+      <c r="E518" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="519" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B519" t="s">
+        <v>12</v>
+      </c>
+      <c r="C519">
+        <v>0</v>
+      </c>
+      <c r="D519">
+        <v>3</v>
+      </c>
+      <c r="E519" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="520" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B520" t="s">
+        <v>5</v>
+      </c>
+      <c r="C520">
+        <v>0</v>
+      </c>
+      <c r="D520">
+        <v>2</v>
+      </c>
+      <c r="E520" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="521" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B521" t="s">
+        <v>14</v>
+      </c>
+      <c r="C521">
+        <v>2</v>
+      </c>
+      <c r="D521">
+        <v>1</v>
+      </c>
+      <c r="E521" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="522" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B522" t="s">
+        <v>13</v>
+      </c>
+      <c r="C522">
+        <v>2</v>
+      </c>
+      <c r="D522">
+        <v>2</v>
+      </c>
+      <c r="E522" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="523" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B523" t="s">
+        <v>9</v>
+      </c>
+      <c r="C523">
+        <v>1</v>
+      </c>
+      <c r="D523">
+        <v>0</v>
+      </c>
+      <c r="E523" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="524" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B524" t="s">
+        <v>11</v>
+      </c>
+      <c r="C524">
+        <v>1</v>
+      </c>
+      <c r="D524">
+        <v>0</v>
+      </c>
+      <c r="E524" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="525" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B525" t="s">
+        <v>8</v>
+      </c>
+      <c r="C525">
+        <v>1</v>
+      </c>
+      <c r="D525">
+        <v>0</v>
+      </c>
+      <c r="E525" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="526" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B526" t="s">
+        <v>7</v>
+      </c>
+      <c r="C526">
+        <v>2</v>
+      </c>
+      <c r="D526">
+        <v>1</v>
+      </c>
+      <c r="E526" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="527" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B527" t="s">
+        <v>15</v>
+      </c>
+      <c r="C527">
+        <v>2</v>
+      </c>
+      <c r="D527">
+        <v>0</v>
+      </c>
+      <c r="E527" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="528" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B528" t="s">
+        <v>6</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+      <c r="D528">
+        <v>1</v>
+      </c>
+      <c r="E528" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="529" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B529" t="s">
+        <v>12</v>
+      </c>
+      <c r="C529">
+        <v>2</v>
+      </c>
+      <c r="D529">
+        <v>1</v>
+      </c>
+      <c r="E529" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="530" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B530" t="s">
+        <v>5</v>
+      </c>
+      <c r="C530">
+        <v>2</v>
+      </c>
+      <c r="D530">
+        <v>1</v>
+      </c>
+      <c r="E530" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="531" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B531" t="s">
+        <v>14</v>
+      </c>
+      <c r="C531">
+        <v>1</v>
+      </c>
+      <c r="D531">
+        <v>2</v>
+      </c>
+      <c r="E531" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="532" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B532" t="s">
+        <v>13</v>
+      </c>
+      <c r="C532">
+        <v>3</v>
+      </c>
+      <c r="D532">
+        <v>3</v>
+      </c>
+      <c r="E532" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="533" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B533" t="s">
+        <v>9</v>
+      </c>
+      <c r="C533">
+        <v>0</v>
+      </c>
+      <c r="D533">
+        <v>2</v>
+      </c>
+      <c r="E533" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="534" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B534" t="s">
+        <v>11</v>
+      </c>
+      <c r="C534">
+        <v>1</v>
+      </c>
+      <c r="D534">
+        <v>3</v>
+      </c>
+      <c r="E534" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="535" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B535" t="s">
+        <v>8</v>
+      </c>
+      <c r="C535">
+        <v>2</v>
+      </c>
+      <c r="D535">
+        <v>3</v>
+      </c>
+      <c r="E535" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="536" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B536" t="s">
+        <v>7</v>
+      </c>
+      <c r="C536">
+        <v>1</v>
+      </c>
+      <c r="D536">
+        <v>2</v>
+      </c>
+      <c r="E536" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="537" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B537" t="s">
+        <v>15</v>
+      </c>
+      <c r="C537">
+        <v>1</v>
+      </c>
+      <c r="D537">
+        <v>1</v>
+      </c>
+      <c r="E537" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="538" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B538" t="s">
+        <v>6</v>
+      </c>
+      <c r="C538">
+        <v>1</v>
+      </c>
+      <c r="D538">
+        <v>1</v>
+      </c>
+      <c r="E538" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="539" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B539" t="s">
+        <v>12</v>
+      </c>
+      <c r="C539">
+        <v>1</v>
+      </c>
+      <c r="D539">
+        <v>2</v>
+      </c>
+      <c r="E539" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="540" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B540" t="s">
+        <v>5</v>
+      </c>
+      <c r="C540">
+        <v>1</v>
+      </c>
+      <c r="D540">
+        <v>2</v>
+      </c>
+      <c r="E540" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="541" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B541" t="s">
+        <v>14</v>
+      </c>
+      <c r="C541">
+        <v>0</v>
+      </c>
+      <c r="D541">
+        <v>1</v>
+      </c>
+      <c r="E541" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="542" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B542" t="s">
+        <v>13</v>
+      </c>
+      <c r="C542">
+        <v>1</v>
+      </c>
+      <c r="D542">
+        <v>0</v>
+      </c>
+      <c r="E542" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="543" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B543" t="s">
+        <v>9</v>
+      </c>
+      <c r="C543">
+        <v>0</v>
+      </c>
+      <c r="D543">
+        <v>1</v>
+      </c>
+      <c r="E543" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="544" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B544" t="s">
+        <v>11</v>
+      </c>
+      <c r="C544">
+        <v>2</v>
+      </c>
+      <c r="D544">
+        <v>0</v>
+      </c>
+      <c r="E544" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="545" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B545" t="s">
+        <v>8</v>
+      </c>
+      <c r="C545">
+        <v>2</v>
+      </c>
+      <c r="D545">
+        <v>1</v>
+      </c>
+      <c r="E545" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="546" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B546" t="s">
+        <v>7</v>
+      </c>
+      <c r="C546">
+        <v>1</v>
+      </c>
+      <c r="D546">
+        <v>0</v>
+      </c>
+      <c r="E546" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="547" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B547" t="s">
+        <v>15</v>
+      </c>
+      <c r="C547">
+        <v>1</v>
+      </c>
+      <c r="D547">
+        <v>0</v>
+      </c>
+      <c r="E547" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="548" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B548" t="s">
+        <v>6</v>
+      </c>
+      <c r="C548">
+        <v>1</v>
+      </c>
+      <c r="D548">
+        <v>0</v>
+      </c>
+      <c r="E548" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="549" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B549" t="s">
+        <v>12</v>
+      </c>
+      <c r="C549">
+        <v>2</v>
+      </c>
+      <c r="D549">
+        <v>0</v>
+      </c>
+      <c r="E549" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="550" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B550" t="s">
+        <v>5</v>
+      </c>
+      <c r="C550">
+        <v>1</v>
+      </c>
+      <c r="D550">
+        <v>0</v>
+      </c>
+      <c r="E550" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="551" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B551" t="s">
+        <v>14</v>
+      </c>
+      <c r="C551">
+        <v>0</v>
+      </c>
+      <c r="D551">
+        <v>3</v>
+      </c>
+      <c r="E551" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="552" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B552" t="s">
+        <v>13</v>
+      </c>
+      <c r="C552">
+        <v>0</v>
+      </c>
+      <c r="D552">
+        <v>6</v>
+      </c>
+      <c r="E552" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="553" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B553" t="s">
+        <v>9</v>
+      </c>
+      <c r="C553">
+        <v>0</v>
+      </c>
+      <c r="D553">
+        <v>3</v>
+      </c>
+      <c r="E553" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="554" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B554" t="s">
+        <v>11</v>
+      </c>
+      <c r="C554">
+        <v>0</v>
+      </c>
+      <c r="D554">
+        <v>3</v>
+      </c>
+      <c r="E554" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="555" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B555" t="s">
+        <v>8</v>
+      </c>
+      <c r="C555">
+        <v>0</v>
+      </c>
+      <c r="D555">
+        <v>2</v>
+      </c>
+      <c r="E555" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="556" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B556" t="s">
+        <v>7</v>
+      </c>
+      <c r="C556">
+        <v>0</v>
+      </c>
+      <c r="D556">
+        <v>4</v>
+      </c>
+      <c r="E556" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="557" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B557" t="s">
+        <v>15</v>
+      </c>
+      <c r="C557">
+        <v>0</v>
+      </c>
+      <c r="D557">
+        <v>4</v>
+      </c>
+      <c r="E557" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="558" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B558" t="s">
+        <v>6</v>
+      </c>
+      <c r="C558">
+        <v>0</v>
+      </c>
+      <c r="D558">
+        <v>2</v>
+      </c>
+      <c r="E558" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="559" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B559" t="s">
+        <v>12</v>
+      </c>
+      <c r="C559">
+        <v>0</v>
+      </c>
+      <c r="D559">
+        <v>3</v>
+      </c>
+      <c r="E559" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="560" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B560" t="s">
+        <v>5</v>
+      </c>
+      <c r="C560">
+        <v>0</v>
+      </c>
+      <c r="D560">
+        <v>3</v>
+      </c>
+      <c r="E560" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="561" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B561" t="s">
+        <v>14</v>
+      </c>
+      <c r="C561">
+        <v>2</v>
+      </c>
+      <c r="D561">
+        <v>1</v>
+      </c>
+      <c r="E561" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="562" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B562" t="s">
+        <v>13</v>
+      </c>
+      <c r="C562">
+        <v>1</v>
+      </c>
+      <c r="D562">
+        <v>0</v>
+      </c>
+      <c r="E562" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="563" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B563" t="s">
+        <v>9</v>
+      </c>
+      <c r="C563">
+        <v>1</v>
+      </c>
+      <c r="D563">
+        <v>0</v>
+      </c>
+      <c r="E563" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="564" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B564" t="s">
+        <v>11</v>
+      </c>
+      <c r="C564">
+        <v>0</v>
+      </c>
+      <c r="D564">
+        <v>1</v>
+      </c>
+      <c r="E564" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="565" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B565" t="s">
+        <v>8</v>
+      </c>
+      <c r="C565">
+        <v>1</v>
+      </c>
+      <c r="D565">
+        <v>2</v>
+      </c>
+      <c r="E565" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="566" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B566" t="s">
+        <v>7</v>
+      </c>
+      <c r="C566">
+        <v>1</v>
+      </c>
+      <c r="D566">
+        <v>1</v>
+      </c>
+      <c r="E566" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="567" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B567" t="s">
+        <v>15</v>
+      </c>
+      <c r="C567">
+        <v>1</v>
+      </c>
+      <c r="D567">
+        <v>2</v>
+      </c>
+      <c r="E567" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="568" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B568" t="s">
+        <v>6</v>
+      </c>
+      <c r="C568">
+        <v>1</v>
+      </c>
+      <c r="D568">
+        <v>1</v>
+      </c>
+      <c r="E568" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="569" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B569" t="s">
+        <v>12</v>
+      </c>
+      <c r="C569">
+        <v>2</v>
+      </c>
+      <c r="D569">
+        <v>1</v>
+      </c>
+      <c r="E569" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="570" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B570" t="s">
+        <v>5</v>
+      </c>
+      <c r="C570">
+        <v>1</v>
+      </c>
+      <c r="D570">
+        <v>1</v>
+      </c>
+      <c r="E570" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="571" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B571" t="s">
+        <v>11</v>
+      </c>
+      <c r="C571">
+        <v>0</v>
+      </c>
+      <c r="D571">
+        <v>2</v>
+      </c>
+      <c r="E571" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="572" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B572" t="s">
+        <v>13</v>
+      </c>
+      <c r="C572">
+        <v>0</v>
+      </c>
+      <c r="D572">
+        <v>2</v>
+      </c>
+      <c r="E572" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="573" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B573" t="s">
+        <v>8</v>
+      </c>
+      <c r="C573">
+        <v>1</v>
+      </c>
+      <c r="D573">
+        <v>2</v>
+      </c>
+      <c r="E573" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="574" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B574" t="s">
+        <v>15</v>
+      </c>
+      <c r="C574">
+        <v>1</v>
+      </c>
+      <c r="D574">
+        <v>2</v>
+      </c>
+      <c r="E574" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="575" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B575" t="s">
+        <v>5</v>
+      </c>
+      <c r="C575">
+        <v>1</v>
+      </c>
+      <c r="D575">
+        <v>2</v>
+      </c>
+      <c r="E575" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="576" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B576" t="s">
+        <v>14</v>
+      </c>
+      <c r="C576">
+        <v>0</v>
+      </c>
+      <c r="D576">
+        <v>1</v>
+      </c>
+      <c r="E576" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="577" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B577" t="s">
+        <v>6</v>
+      </c>
+      <c r="C577">
+        <v>1</v>
+      </c>
+      <c r="D577">
+        <v>1</v>
+      </c>
+      <c r="E577" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="578" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B578" t="s">
+        <v>11</v>
+      </c>
+      <c r="C578">
+        <v>3</v>
+      </c>
+      <c r="D578">
+        <v>1</v>
+      </c>
+      <c r="E578" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="579" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B579" t="s">
+        <v>8</v>
+      </c>
+      <c r="C579">
+        <v>2</v>
+      </c>
+      <c r="D579">
+        <v>1</v>
+      </c>
+      <c r="E579" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="580" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B580" t="s">
+        <v>14</v>
+      </c>
+      <c r="C580">
+        <v>2</v>
+      </c>
+      <c r="D580">
+        <v>1</v>
+      </c>
+      <c r="E580" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="581" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B581" t="s">
+        <v>6</v>
+      </c>
+      <c r="C581">
+        <v>2</v>
+      </c>
+      <c r="D581">
+        <v>1</v>
+      </c>
+      <c r="E581" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="582" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B582" t="s">
+        <v>10</v>
+      </c>
+      <c r="C582">
+        <v>2</v>
+      </c>
+      <c r="D582">
+        <v>1</v>
+      </c>
+      <c r="E582" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="583" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B583" t="s">
+        <v>12</v>
+      </c>
+      <c r="C583">
+        <v>2</v>
+      </c>
+      <c r="D583">
+        <v>1</v>
+      </c>
+      <c r="E583" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="584" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B584" t="s">
+        <v>9</v>
+      </c>
+      <c r="C584">
+        <v>2</v>
+      </c>
+      <c r="D584">
+        <v>1</v>
+      </c>
+      <c r="E584" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="585" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B585" t="s">
+        <v>15</v>
+      </c>
+      <c r="C585">
+        <v>3</v>
+      </c>
+      <c r="D585">
+        <v>1</v>
+      </c>
+      <c r="E585" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="586" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B586" t="s">
+        <v>7</v>
+      </c>
+      <c r="C586">
+        <v>3</v>
+      </c>
+      <c r="D586">
+        <v>0</v>
+      </c>
+      <c r="E586" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="587" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B587" t="s">
+        <v>5</v>
+      </c>
+      <c r="C587">
+        <v>2</v>
+      </c>
+      <c r="D587">
+        <v>1</v>
+      </c>
+      <c r="E587" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="588" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B588" t="s">
+        <v>13</v>
+      </c>
+      <c r="C588">
+        <v>3</v>
+      </c>
+      <c r="D588">
+        <v>0</v>
+      </c>
+      <c r="E588" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="589" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B589" t="s">
+        <v>8</v>
+      </c>
+      <c r="C589">
+        <v>3</v>
+      </c>
+      <c r="D589">
+        <v>1</v>
+      </c>
+      <c r="E589" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="590" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B590" t="s">
+        <v>11</v>
+      </c>
+      <c r="C590">
+        <v>2</v>
+      </c>
+      <c r="D590">
+        <v>0</v>
+      </c>
+      <c r="E590" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="591" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B591" t="s">
+        <v>14</v>
+      </c>
+      <c r="C591">
+        <v>2</v>
+      </c>
+      <c r="D591">
+        <v>0</v>
+      </c>
+      <c r="E591" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="592" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B592" t="s">
+        <v>6</v>
+      </c>
+      <c r="C592">
+        <v>2</v>
+      </c>
+      <c r="D592">
+        <v>0</v>
+      </c>
+      <c r="E592" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="593" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B593" t="s">
+        <v>10</v>
+      </c>
+      <c r="C593">
+        <v>3</v>
+      </c>
+      <c r="D593">
+        <v>0</v>
+      </c>
+      <c r="E593" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="594" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B594" t="s">
+        <v>12</v>
+      </c>
+      <c r="C594">
+        <v>3</v>
+      </c>
+      <c r="D594">
+        <v>1</v>
+      </c>
+      <c r="E594" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="595" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B595" t="s">
+        <v>9</v>
+      </c>
+      <c r="C595">
+        <v>5</v>
+      </c>
+      <c r="D595">
+        <v>1</v>
+      </c>
+      <c r="E595" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="596" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B596" t="s">
+        <v>15</v>
+      </c>
+      <c r="C596">
+        <v>2</v>
+      </c>
+      <c r="D596">
+        <v>0</v>
+      </c>
+      <c r="E596" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="597" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B597" t="s">
+        <v>7</v>
+      </c>
+      <c r="C597">
+        <v>1</v>
+      </c>
+      <c r="D597">
+        <v>0</v>
+      </c>
+      <c r="E597" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="598" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B598" t="s">
+        <v>5</v>
+      </c>
+      <c r="C598">
+        <v>2</v>
+      </c>
+      <c r="D598">
+        <v>0</v>
+      </c>
+      <c r="E598" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="599" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B599" t="s">
+        <v>13</v>
+      </c>
+      <c r="C599">
+        <v>2</v>
+      </c>
+      <c r="D599">
+        <v>1</v>
+      </c>
+      <c r="E599" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="600" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B600" t="s">
+        <v>8</v>
+      </c>
+      <c r="C600">
+        <v>3</v>
+      </c>
+      <c r="D600">
+        <v>1</v>
+      </c>
+      <c r="E600" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="601" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B601" t="s">
+        <v>11</v>
+      </c>
+      <c r="C601">
+        <v>2</v>
+      </c>
+      <c r="D601">
+        <v>1</v>
+      </c>
+      <c r="E601" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="602" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B602" t="s">
+        <v>14</v>
+      </c>
+      <c r="C602">
+        <v>1</v>
+      </c>
+      <c r="D602">
+        <v>1</v>
+      </c>
+      <c r="E602" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="603" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B603" t="s">
+        <v>6</v>
+      </c>
+      <c r="C603">
+        <v>2</v>
+      </c>
+      <c r="D603">
+        <v>1</v>
+      </c>
+      <c r="E603" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="604" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B604" t="s">
+        <v>10</v>
+      </c>
+      <c r="C604">
+        <v>1</v>
+      </c>
+      <c r="D604">
+        <v>1</v>
+      </c>
+      <c r="E604" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="605" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B605" t="s">
+        <v>12</v>
+      </c>
+      <c r="C605">
+        <v>2</v>
+      </c>
+      <c r="D605">
+        <v>1</v>
+      </c>
+      <c r="E605" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="606" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B606" t="s">
+        <v>9</v>
+      </c>
+      <c r="C606">
+        <v>3</v>
+      </c>
+      <c r="D606">
+        <v>1</v>
+      </c>
+      <c r="E606" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="607" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B607" t="s">
+        <v>15</v>
+      </c>
+      <c r="C607">
+        <v>0</v>
+      </c>
+      <c r="D607">
+        <v>1</v>
+      </c>
+      <c r="E607" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="608" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B608" t="s">
+        <v>7</v>
+      </c>
+      <c r="C608">
+        <v>1</v>
+      </c>
+      <c r="D608">
+        <v>1</v>
+      </c>
+      <c r="E608" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="609" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B609" t="s">
+        <v>13</v>
+      </c>
+      <c r="C609">
+        <v>0</v>
+      </c>
+      <c r="D609">
+        <v>1</v>
+      </c>
+      <c r="E609" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="610" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B610" t="s">
+        <v>5</v>
+      </c>
+      <c r="C610">
+        <v>2</v>
+      </c>
+      <c r="D610">
+        <v>1</v>
+      </c>
+      <c r="E610" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="611" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B611" t="s">
+        <v>8</v>
+      </c>
+      <c r="C611">
+        <v>0</v>
+      </c>
+      <c r="D611">
+        <v>2</v>
+      </c>
+      <c r="E611" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="612" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B612" t="s">
+        <v>6</v>
+      </c>
+      <c r="C612">
+        <v>1</v>
+      </c>
+      <c r="D612">
+        <v>2</v>
+      </c>
+      <c r="E612" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="613" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B613" t="s">
+        <v>12</v>
+      </c>
+      <c r="C613">
+        <v>0</v>
+      </c>
+      <c r="D613">
+        <v>2</v>
+      </c>
+      <c r="E613" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="614" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B614" t="s">
+        <v>15</v>
+      </c>
+      <c r="C614">
+        <v>0</v>
+      </c>
+      <c r="D614">
+        <v>2</v>
+      </c>
+      <c r="E614" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="615" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B615" t="s">
+        <v>13</v>
+      </c>
+      <c r="C615">
+        <v>2</v>
+      </c>
+      <c r="D615">
+        <v>1</v>
+      </c>
+      <c r="E615" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="616" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B616" t="s">
+        <v>11</v>
+      </c>
+      <c r="C616">
+        <v>1</v>
+      </c>
+      <c r="D616">
+        <v>3</v>
+      </c>
+      <c r="E616" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="617" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B617" t="s">
+        <v>14</v>
+      </c>
+      <c r="C617">
+        <v>1</v>
+      </c>
+      <c r="D617">
+        <v>2</v>
+      </c>
+      <c r="E617" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="618" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B618" t="s">
+        <v>9</v>
+      </c>
+      <c r="C618">
+        <v>1</v>
+      </c>
+      <c r="D618">
+        <v>2</v>
+      </c>
+      <c r="E618" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="619" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B619" t="s">
+        <v>10</v>
+      </c>
+      <c r="C619">
+        <v>0</v>
+      </c>
+      <c r="D619">
+        <v>2</v>
+      </c>
+      <c r="E619" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="620" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B620" t="s">
+        <v>7</v>
+      </c>
+      <c r="C620">
+        <v>2</v>
+      </c>
+      <c r="D620">
+        <v>2</v>
+      </c>
+      <c r="E620" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="621" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B621" t="s">
+        <v>5</v>
+      </c>
+      <c r="C621">
+        <v>1</v>
+      </c>
+      <c r="D621">
+        <v>2</v>
+      </c>
+      <c r="E621" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="622" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B622" t="s">
+        <v>8</v>
+      </c>
+      <c r="C622">
+        <v>3</v>
+      </c>
+      <c r="D622">
+        <v>0</v>
+      </c>
+      <c r="E622" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="623" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B623" t="s">
+        <v>14</v>
+      </c>
+      <c r="C623">
+        <v>2</v>
+      </c>
+      <c r="D623">
+        <v>0</v>
+      </c>
+      <c r="E623" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="624" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B624" t="s">
+        <v>6</v>
+      </c>
+      <c r="C624">
+        <v>2</v>
+      </c>
+      <c r="D624">
+        <v>1</v>
+      </c>
+      <c r="E624" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="625" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B625" t="s">
+        <v>12</v>
+      </c>
+      <c r="C625">
+        <v>3</v>
+      </c>
+      <c r="D625">
+        <v>1</v>
+      </c>
+      <c r="E625" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="626" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B626" t="s">
+        <v>15</v>
+      </c>
+      <c r="C626">
+        <v>2</v>
+      </c>
+      <c r="D626">
+        <v>0</v>
+      </c>
+      <c r="E626" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="627" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B627" t="s">
+        <v>11</v>
+      </c>
+      <c r="C627">
+        <v>4</v>
+      </c>
+      <c r="D627">
+        <v>0</v>
+      </c>
+      <c r="E627" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="628" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B628" t="s">
+        <v>9</v>
+      </c>
+      <c r="C628">
+        <v>3</v>
+      </c>
+      <c r="D628">
+        <v>1</v>
+      </c>
+      <c r="E628" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="629" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B629" t="s">
+        <v>10</v>
+      </c>
+      <c r="C629">
+        <v>3</v>
+      </c>
+      <c r="D629">
+        <v>1</v>
+      </c>
+      <c r="E629" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="630" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B630" t="s">
+        <v>7</v>
+      </c>
+      <c r="C630">
+        <v>2</v>
+      </c>
+      <c r="D630">
+        <v>0</v>
+      </c>
+      <c r="E630" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="631" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B631" t="s">
+        <v>5</v>
+      </c>
+      <c r="C631">
+        <v>2</v>
+      </c>
+      <c r="D631">
+        <v>0</v>
+      </c>
+      <c r="E631" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="632" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B632" t="s">
+        <v>8</v>
+      </c>
+      <c r="C632">
+        <v>2</v>
+      </c>
+      <c r="D632">
+        <v>1</v>
+      </c>
+      <c r="E632" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="633" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B633" t="s">
+        <v>14</v>
+      </c>
+      <c r="C633">
+        <v>1</v>
+      </c>
+      <c r="D633">
+        <v>1</v>
+      </c>
+      <c r="E633" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="634" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B634" t="s">
+        <v>6</v>
+      </c>
+      <c r="C634">
+        <v>1</v>
+      </c>
+      <c r="D634">
+        <v>0</v>
+      </c>
+      <c r="E634" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="635" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B635" t="s">
+        <v>12</v>
+      </c>
+      <c r="C635">
+        <v>1</v>
+      </c>
+      <c r="D635">
+        <v>0</v>
+      </c>
+      <c r="E635" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="636" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B636" t="s">
+        <v>15</v>
+      </c>
+      <c r="C636">
+        <v>1</v>
+      </c>
+      <c r="D636">
+        <v>0</v>
+      </c>
+      <c r="E636" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="637" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B637" t="s">
+        <v>11</v>
+      </c>
+      <c r="C637">
+        <v>2</v>
+      </c>
+      <c r="D637">
+        <v>0</v>
+      </c>
+      <c r="E637" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="638" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B638" t="s">
+        <v>9</v>
+      </c>
+      <c r="C638">
+        <v>1</v>
+      </c>
+      <c r="D638">
+        <v>1</v>
+      </c>
+      <c r="E638" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="639" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B639" t="s">
+        <v>10</v>
+      </c>
+      <c r="C639">
+        <v>1</v>
+      </c>
+      <c r="D639">
+        <v>1</v>
+      </c>
+      <c r="E639" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="640" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B640" t="s">
+        <v>7</v>
+      </c>
+      <c r="C640">
+        <v>1</v>
+      </c>
+      <c r="D640">
+        <v>1</v>
+      </c>
+      <c r="E640" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B641" t="s">
+        <v>5</v>
+      </c>
+      <c r="C641">
+        <v>1</v>
+      </c>
+      <c r="D641">
+        <v>1</v>
+      </c>
+      <c r="E641" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="642" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B642" t="s">
+        <v>13</v>
+      </c>
+      <c r="C642">
+        <v>1</v>
+      </c>
+      <c r="D642">
+        <v>1</v>
+      </c>
+      <c r="E642" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="643" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B643" t="s">
+        <v>8</v>
+      </c>
+      <c r="C643">
+        <v>3</v>
+      </c>
+      <c r="D643">
+        <v>1</v>
+      </c>
+      <c r="E643" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="644" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B644" t="s">
+        <v>14</v>
+      </c>
+      <c r="C644">
+        <v>3</v>
+      </c>
+      <c r="D644">
+        <v>0</v>
+      </c>
+      <c r="E644" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="645" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B645" t="s">
+        <v>12</v>
+      </c>
+      <c r="C645">
+        <v>2</v>
+      </c>
+      <c r="D645">
+        <v>0</v>
+      </c>
+      <c r="E645" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="646" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B646" t="s">
+        <v>15</v>
+      </c>
+      <c r="C646">
+        <v>3</v>
+      </c>
+      <c r="D646">
+        <v>0</v>
+      </c>
+      <c r="E646" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="647" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B647" t="s">
+        <v>11</v>
+      </c>
+      <c r="C647">
+        <v>1</v>
+      </c>
+      <c r="D647">
+        <v>0</v>
+      </c>
+      <c r="E647" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="648" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B648" t="s">
+        <v>9</v>
+      </c>
+      <c r="C648">
+        <v>2</v>
+      </c>
+      <c r="D648">
+        <v>0</v>
+      </c>
+      <c r="E648" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="649" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B649" t="s">
+        <v>13</v>
+      </c>
+      <c r="C649">
+        <v>2</v>
+      </c>
+      <c r="D649">
+        <v>1</v>
+      </c>
+      <c r="E649" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="650" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B650" t="s">
+        <v>6</v>
+      </c>
+      <c r="C650">
+        <v>2</v>
+      </c>
+      <c r="D650">
+        <v>0</v>
+      </c>
+      <c r="E650" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="651" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B651" t="s">
+        <v>10</v>
+      </c>
+      <c r="C651">
+        <v>2</v>
+      </c>
+      <c r="D651">
+        <v>0</v>
+      </c>
+      <c r="E651" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="652" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B652" t="s">
+        <v>7</v>
+      </c>
+      <c r="C652">
+        <v>2</v>
+      </c>
+      <c r="D652">
+        <v>1</v>
+      </c>
+      <c r="E652" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="653" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B653" t="s">
+        <v>8</v>
+      </c>
+      <c r="C653">
+        <v>1</v>
+      </c>
+      <c r="D653">
+        <v>2</v>
+      </c>
+      <c r="E653" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="654" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B654" t="s">
+        <v>14</v>
+      </c>
+      <c r="C654">
+        <v>2</v>
+      </c>
+      <c r="D654">
+        <v>1</v>
+      </c>
+      <c r="E654" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="655" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B655" t="s">
+        <v>12</v>
+      </c>
+      <c r="C655">
+        <v>2</v>
+      </c>
+      <c r="D655">
+        <v>1</v>
+      </c>
+      <c r="E655" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="656" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B656" t="s">
+        <v>15</v>
+      </c>
+      <c r="C656">
+        <v>2</v>
+      </c>
+      <c r="D656">
+        <v>0</v>
+      </c>
+      <c r="E656" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="657" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B657" t="s">
+        <v>11</v>
+      </c>
+      <c r="C657">
+        <v>1</v>
+      </c>
+      <c r="D657">
+        <v>2</v>
+      </c>
+      <c r="E657" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="658" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B658" t="s">
+        <v>9</v>
+      </c>
+      <c r="C658">
+        <v>3</v>
+      </c>
+      <c r="D658">
+        <v>1</v>
+      </c>
+      <c r="E658" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="659" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B659" t="s">
+        <v>13</v>
+      </c>
+      <c r="C659">
+        <v>1</v>
+      </c>
+      <c r="D659">
+        <v>1</v>
+      </c>
+      <c r="E659" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="660" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B660" t="s">
+        <v>6</v>
+      </c>
+      <c r="C660">
+        <v>2</v>
+      </c>
+      <c r="D660">
+        <v>1</v>
+      </c>
+      <c r="E660" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="661" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B661" t="s">
+        <v>10</v>
+      </c>
+      <c r="C661">
+        <v>1</v>
+      </c>
+      <c r="D661">
+        <v>1</v>
+      </c>
+      <c r="E661" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="662" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B662" t="s">
+        <v>7</v>
+      </c>
+      <c r="C662">
+        <v>1</v>
+      </c>
+      <c r="D662">
+        <v>1</v>
+      </c>
+      <c r="E662" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="663" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B663" t="s">
+        <v>5</v>
+      </c>
+      <c r="C663">
+        <v>1</v>
+      </c>
+      <c r="D663">
+        <v>1</v>
+      </c>
+      <c r="E663" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="664" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B664" t="s">
+        <v>8</v>
+      </c>
+      <c r="C664">
+        <v>3</v>
+      </c>
+      <c r="D664">
+        <v>1</v>
+      </c>
+      <c r="E664" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="665" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B665" t="s">
+        <v>14</v>
+      </c>
+      <c r="C665">
+        <v>2</v>
+      </c>
+      <c r="D665">
+        <v>0</v>
+      </c>
+      <c r="E665" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="666" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B666" t="s">
+        <v>12</v>
+      </c>
+      <c r="C666">
+        <v>2</v>
+      </c>
+      <c r="D666">
+        <v>0</v>
+      </c>
+      <c r="E666" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="667" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B667" t="s">
+        <v>15</v>
+      </c>
+      <c r="C667">
+        <v>2</v>
+      </c>
+      <c r="D667">
+        <v>1</v>
+      </c>
+      <c r="E667" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="668" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B668" t="s">
+        <v>11</v>
+      </c>
+      <c r="C668">
+        <v>2</v>
+      </c>
+      <c r="D668">
+        <v>1</v>
+      </c>
+      <c r="E668" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="669" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B669" t="s">
+        <v>9</v>
+      </c>
+      <c r="C669">
+        <v>2</v>
+      </c>
+      <c r="D669">
+        <v>0</v>
+      </c>
+      <c r="E669" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="670" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B670" t="s">
+        <v>13</v>
+      </c>
+      <c r="C670">
+        <v>2</v>
+      </c>
+      <c r="D670">
+        <v>0</v>
+      </c>
+      <c r="E670" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="671" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B671" t="s">
+        <v>6</v>
+      </c>
+      <c r="C671">
+        <v>2</v>
+      </c>
+      <c r="D671">
+        <v>1</v>
+      </c>
+      <c r="E671" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="672" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B672" t="s">
+        <v>10</v>
+      </c>
+      <c r="C672">
+        <v>1</v>
+      </c>
+      <c r="D672">
+        <v>2</v>
+      </c>
+      <c r="E672" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="673" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B673" t="s">
+        <v>7</v>
+      </c>
+      <c r="C673">
+        <v>2</v>
+      </c>
+      <c r="D673">
+        <v>1</v>
+      </c>
+      <c r="E673" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="674" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B674" t="s">
+        <v>5</v>
+      </c>
+      <c r="C674">
+        <v>2</v>
+      </c>
+      <c r="D674">
+        <v>0</v>
+      </c>
+      <c r="E674" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="675" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B675" t="s">
+        <v>8</v>
+      </c>
+      <c r="C675">
+        <v>3</v>
+      </c>
+      <c r="D675">
+        <v>1</v>
+      </c>
+      <c r="E675" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="676" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B676" t="s">
+        <v>14</v>
+      </c>
+      <c r="C676">
+        <v>2</v>
+      </c>
+      <c r="D676">
+        <v>0</v>
+      </c>
+      <c r="E676" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="677" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B677" t="s">
+        <v>12</v>
+      </c>
+      <c r="C677">
+        <v>2</v>
+      </c>
+      <c r="D677">
+        <v>1</v>
+      </c>
+      <c r="E677" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="678" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B678" t="s">
+        <v>15</v>
+      </c>
+      <c r="C678">
+        <v>2</v>
+      </c>
+      <c r="D678">
+        <v>0</v>
+      </c>
+      <c r="E678" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="679" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B679" t="s">
+        <v>11</v>
+      </c>
+      <c r="C679">
+        <v>0</v>
+      </c>
+      <c r="D679">
+        <v>2</v>
+      </c>
+      <c r="E679" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="680" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B680" t="s">
+        <v>9</v>
+      </c>
+      <c r="C680">
+        <v>2</v>
+      </c>
+      <c r="D680">
+        <v>0</v>
+      </c>
+      <c r="E680" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="681" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B681" t="s">
+        <v>13</v>
+      </c>
+      <c r="C681">
+        <v>3</v>
+      </c>
+      <c r="D681">
+        <v>1</v>
+      </c>
+      <c r="E681" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="682" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B682" t="s">
+        <v>6</v>
+      </c>
+      <c r="C682">
+        <v>2</v>
+      </c>
+      <c r="D682">
+        <v>1</v>
+      </c>
+      <c r="E682" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="683" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B683" t="s">
+        <v>10</v>
+      </c>
+      <c r="C683">
+        <v>2</v>
+      </c>
+      <c r="D683">
+        <v>1</v>
+      </c>
+      <c r="E683" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="684" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B684" t="s">
+        <v>5</v>
+      </c>
+      <c r="C684">
+        <v>2</v>
+      </c>
+      <c r="D684">
+        <v>1</v>
+      </c>
+      <c r="E684" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="685" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B685" t="s">
+        <v>7</v>
+      </c>
+      <c r="C685">
+        <v>2</v>
+      </c>
+      <c r="D685">
+        <v>1</v>
+      </c>
+      <c r="E685" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="686" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B686" t="s">
+        <v>8</v>
+      </c>
+      <c r="C686">
+        <v>2</v>
+      </c>
+      <c r="D686">
+        <v>1</v>
+      </c>
+      <c r="E686" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="687" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B687" t="s">
+        <v>14</v>
+      </c>
+      <c r="C687">
+        <v>1</v>
+      </c>
+      <c r="D687">
+        <v>1</v>
+      </c>
+      <c r="E687" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="688" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B688" t="s">
+        <v>12</v>
+      </c>
+      <c r="C688">
+        <v>2</v>
+      </c>
+      <c r="D688">
+        <v>1</v>
+      </c>
+      <c r="E688" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="689" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B689" t="s">
+        <v>15</v>
+      </c>
+      <c r="C689">
+        <v>2</v>
+      </c>
+      <c r="D689">
+        <v>1</v>
+      </c>
+      <c r="E689" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="690" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B690" t="s">
+        <v>11</v>
+      </c>
+      <c r="C690">
+        <v>2</v>
+      </c>
+      <c r="D690">
+        <v>1</v>
+      </c>
+      <c r="E690" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="691" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B691" t="s">
+        <v>9</v>
+      </c>
+      <c r="C691">
+        <v>1</v>
+      </c>
+      <c r="D691">
+        <v>2</v>
+      </c>
+      <c r="E691" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="692" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B692" t="s">
+        <v>13</v>
+      </c>
+      <c r="C692">
+        <v>0</v>
+      </c>
+      <c r="D692">
+        <v>0</v>
+      </c>
+      <c r="E692" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="693" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B693" t="s">
+        <v>6</v>
+      </c>
+      <c r="C693">
+        <v>1</v>
+      </c>
+      <c r="D693">
+        <v>1</v>
+      </c>
+      <c r="E693" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="694" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B694" t="s">
+        <v>10</v>
+      </c>
+      <c r="C694">
+        <v>1</v>
+      </c>
+      <c r="D694">
+        <v>1</v>
+      </c>
+      <c r="E694" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="695" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B695" t="s">
+        <v>5</v>
+      </c>
+      <c r="C695">
+        <v>2</v>
+      </c>
+      <c r="D695">
+        <v>1</v>
+      </c>
+      <c r="E695" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="696" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B696" t="s">
+        <v>7</v>
+      </c>
+      <c r="C696">
+        <v>2</v>
+      </c>
+      <c r="D696">
+        <v>2</v>
+      </c>
+      <c r="E696" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="697" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B697" t="s">
+        <v>8</v>
+      </c>
+      <c r="C697">
+        <v>2</v>
+      </c>
+      <c r="D697">
+        <v>1</v>
+      </c>
+      <c r="E697" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="698" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B698" t="s">
+        <v>14</v>
+      </c>
+      <c r="C698">
+        <v>1</v>
+      </c>
+      <c r="D698">
+        <v>0</v>
+      </c>
+      <c r="E698" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="699" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B699" t="s">
+        <v>12</v>
+      </c>
+      <c r="C699">
+        <v>1</v>
+      </c>
+      <c r="D699">
+        <v>0</v>
+      </c>
+      <c r="E699" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="700" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B700" t="s">
+        <v>15</v>
+      </c>
+      <c r="C700">
+        <v>1</v>
+      </c>
+      <c r="D700">
+        <v>1</v>
+      </c>
+      <c r="E700" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="701" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B701" t="s">
+        <v>9</v>
+      </c>
+      <c r="C701">
+        <v>0</v>
+      </c>
+      <c r="D701">
+        <v>1</v>
+      </c>
+      <c r="E701" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="702" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B702" t="s">
+        <v>13</v>
+      </c>
+      <c r="C702">
+        <v>1</v>
+      </c>
+      <c r="D702">
+        <v>0</v>
+      </c>
+      <c r="E702" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="703" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B703" t="s">
+        <v>11</v>
+      </c>
+      <c r="C703">
+        <v>1</v>
+      </c>
+      <c r="D703">
+        <v>1</v>
+      </c>
+      <c r="E703" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="704" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B704" t="s">
+        <v>10</v>
+      </c>
+      <c r="C704">
+        <v>2</v>
+      </c>
+      <c r="D704">
+        <v>0</v>
+      </c>
+      <c r="E704" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B705" t="s">
+        <v>5</v>
+      </c>
+      <c r="C705">
+        <v>2</v>
+      </c>
+      <c r="D705">
+        <v>0</v>
+      </c>
+      <c r="E705" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B706" t="s">
+        <v>6</v>
+      </c>
+      <c r="C706">
+        <v>2</v>
+      </c>
+      <c r="D706">
+        <v>1</v>
+      </c>
+      <c r="E706" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B707" t="s">
+        <v>7</v>
+      </c>
+      <c r="C707">
+        <v>2</v>
+      </c>
+      <c r="D707">
+        <v>2</v>
+      </c>
+      <c r="E707" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B708" t="s">
+        <v>8</v>
+      </c>
+      <c r="C708">
+        <v>1</v>
+      </c>
+      <c r="D708">
+        <v>2</v>
+      </c>
+      <c r="E708" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B709" t="s">
+        <v>14</v>
+      </c>
+      <c r="C709">
+        <v>1</v>
+      </c>
+      <c r="D709">
+        <v>1</v>
+      </c>
+      <c r="E709" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B710" t="s">
+        <v>12</v>
+      </c>
+      <c r="C710">
+        <v>0</v>
+      </c>
+      <c r="D710">
+        <v>2</v>
+      </c>
+      <c r="E710" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B711" t="s">
+        <v>15</v>
+      </c>
+      <c r="C711">
+        <v>0</v>
+      </c>
+      <c r="D711">
+        <v>2</v>
+      </c>
+      <c r="E711" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B712" t="s">
+        <v>9</v>
+      </c>
+      <c r="C712">
+        <v>0</v>
+      </c>
+      <c r="D712">
+        <v>1</v>
+      </c>
+      <c r="E712" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B713" t="s">
+        <v>13</v>
+      </c>
+      <c r="C713">
+        <v>0</v>
+      </c>
+      <c r="D713">
+        <v>2</v>
+      </c>
+      <c r="E713" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B714" t="s">
+        <v>11</v>
+      </c>
+      <c r="C714">
+        <v>0</v>
+      </c>
+      <c r="D714">
+        <v>2</v>
+      </c>
+      <c r="E714" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B715" t="s">
+        <v>10</v>
+      </c>
+      <c r="C715">
+        <v>1</v>
+      </c>
+      <c r="D715">
+        <v>1</v>
+      </c>
+      <c r="E715" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B716" t="s">
+        <v>5</v>
+      </c>
+      <c r="C716">
+        <v>1</v>
+      </c>
+      <c r="D716">
+        <v>2</v>
+      </c>
+      <c r="E716" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B717" t="s">
+        <v>7</v>
+      </c>
+      <c r="C717">
+        <v>0</v>
+      </c>
+      <c r="D717">
+        <v>2</v>
+      </c>
+      <c r="E717" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B718" t="s">
+        <v>6</v>
+      </c>
+      <c r="C718">
+        <v>2</v>
+      </c>
+      <c r="D718">
+        <v>2</v>
+      </c>
+      <c r="E718" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A719" s="2">
+        <v>46201.415613425925</v>
+      </c>
+      <c r="B719" t="s">
+        <v>8</v>
+      </c>
+      <c r="C719">
+        <v>3</v>
+      </c>
+      <c r="D719">
+        <v>1</v>
+      </c>
+      <c r="E719" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A720" s="2">
+        <v>46201.56145833333</v>
+      </c>
+      <c r="B720" t="s">
+        <v>14</v>
+      </c>
+      <c r="C720">
+        <v>3</v>
+      </c>
+      <c r="D720">
+        <v>0</v>
+      </c>
+      <c r="E720" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A721" s="2">
+        <v>46201.875405092593</v>
+      </c>
+      <c r="B721" t="s">
+        <v>12</v>
+      </c>
+      <c r="C721">
+        <v>2</v>
+      </c>
+      <c r="D721">
+        <v>0</v>
+      </c>
+      <c r="E721" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A722" s="2">
+        <v>46202.392395833333</v>
+      </c>
+      <c r="B722" t="s">
+        <v>15</v>
+      </c>
+      <c r="C722">
+        <v>4</v>
+      </c>
+      <c r="D722">
+        <v>0</v>
+      </c>
+      <c r="E722" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A723" s="2">
+        <v>46203.548402777778</v>
+      </c>
+      <c r="B723" t="s">
+        <v>9</v>
+      </c>
+      <c r="C723">
+        <v>2</v>
+      </c>
+      <c r="D723">
+        <v>0</v>
+      </c>
+      <c r="E723" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A724" s="2">
+        <v>46203.834745370368</v>
+      </c>
+      <c r="B724" t="s">
+        <v>13</v>
+      </c>
+      <c r="C724">
+        <v>3</v>
+      </c>
+      <c r="D724">
+        <v>0</v>
+      </c>
+      <c r="E724" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A725" s="2">
+        <v>46204.93240740741</v>
+      </c>
+      <c r="B725" t="s">
+        <v>11</v>
+      </c>
+      <c r="C725">
+        <v>3</v>
+      </c>
+      <c r="D725">
+        <v>0</v>
+      </c>
+      <c r="E725" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A726" s="2">
+        <v>46204.949699074074</v>
+      </c>
+      <c r="B726" t="s">
+        <v>10</v>
+      </c>
+      <c r="C726">
+        <v>1</v>
+      </c>
+      <c r="D726">
+        <v>2</v>
+      </c>
+      <c r="E726" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A727" s="2">
+        <v>46206.433611111112</v>
+      </c>
+      <c r="B727" t="s">
+        <v>7</v>
+      </c>
+      <c r="C727">
+        <v>4</v>
+      </c>
+      <c r="D727">
+        <v>1</v>
+      </c>
+      <c r="E727" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A728" s="2">
+        <v>46206.473182870373</v>
+      </c>
+      <c r="B728" t="s">
+        <v>6</v>
+      </c>
+      <c r="C728">
+        <v>4</v>
+      </c>
+      <c r="D728">
+        <v>0</v>
+      </c>
+      <c r="E728" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A729" s="2">
+        <v>46206.790543981479</v>
+      </c>
+      <c r="B729" t="s">
+        <v>5</v>
+      </c>
+      <c r="C729">
+        <v>3</v>
+      </c>
+      <c r="D729">
+        <v>0</v>
+      </c>
+      <c r="E729" t="s">
         <v>17</v>
       </c>
     </row>

--- a/historico_pdf.xlsx
+++ b/historico_pdf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c35027b\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E29C491-88D2-4822-AF5B-A27E54294396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0DF8E5A-88DB-4BEF-8E4E-DA11C28DCD7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="86">
   <si>
     <t>data_registro</t>
   </si>
@@ -272,6 +272,12 @@
   </si>
   <si>
     <t>Jordânia x Argélia</t>
+  </si>
+  <si>
+    <t>Portugal x Espanha</t>
+  </si>
+  <si>
+    <t>Estados Unidos x Bélgica</t>
   </si>
 </sst>
 </file>
@@ -640,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E729"/>
+  <dimension ref="A1:E731"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -11153,6 +11159,34 @@
         <v>17</v>
       </c>
     </row>
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B730" t="s">
+        <v>5</v>
+      </c>
+      <c r="C730">
+        <v>1</v>
+      </c>
+      <c r="D730">
+        <v>2</v>
+      </c>
+      <c r="E730" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B731" t="s">
+        <v>5</v>
+      </c>
+      <c r="C731">
+        <v>1</v>
+      </c>
+      <c r="D731">
+        <v>2</v>
+      </c>
+      <c r="E731" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
